--- a/outputs/scenario_campaigns_20260716/02_keywords_staging_artifact.xlsx
+++ b/outputs/scenario_campaigns_20260716/02_keywords_staging_artifact.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet0" sheetId="1" r:id="R5b87fb2390874217"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet0" sheetId="1" r:id="R03f77233ceae4de6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -313,13 +313,13 @@
       </x:c>
       <x:c r="H2"/>
       <x:c r="I2" t="str">
-        <x:v>critical infrastructure anti drone</x:v>
+        <x:v>government building anti drone</x:v>
       </x:c>
       <x:c r="J2" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K2" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L2"/>
       <x:c r="M2"/>
@@ -351,13 +351,13 @@
       </x:c>
       <x:c r="H3"/>
       <x:c r="I3" t="str">
-        <x:v>critical infrastructure drone detection</x:v>
+        <x:v>data center drone detection</x:v>
       </x:c>
       <x:c r="J3" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K3" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L3"/>
       <x:c r="M3"/>
@@ -389,13 +389,13 @@
       </x:c>
       <x:c r="H4"/>
       <x:c r="I4" t="str">
-        <x:v>critical infrastructure c-uas</x:v>
+        <x:v>telecom tower drone detector</x:v>
       </x:c>
       <x:c r="J4" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K4" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L4"/>
       <x:c r="M4"/>
@@ -427,13 +427,13 @@
       </x:c>
       <x:c r="H5"/>
       <x:c r="I5" t="str">
-        <x:v>critical infrastructure drone detector</x:v>
+        <x:v>water treatment plant anti drone</x:v>
       </x:c>
       <x:c r="J5" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K5" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L5"/>
       <x:c r="M5"/>
@@ -465,13 +465,13 @@
       </x:c>
       <x:c r="H6"/>
       <x:c r="I6" t="str">
-        <x:v>critical infrastructure airspace monitoring</x:v>
+        <x:v>dam drone detection</x:v>
       </x:c>
       <x:c r="J6" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K6" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L6"/>
       <x:c r="M6"/>
@@ -503,13 +503,13 @@
       </x:c>
       <x:c r="H7"/>
       <x:c r="I7" t="str">
-        <x:v>critical infrastructure counter drone</x:v>
+        <x:v>railway station anti drone</x:v>
       </x:c>
       <x:c r="J7" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K7" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L7"/>
       <x:c r="M7"/>
@@ -541,13 +541,13 @@
       </x:c>
       <x:c r="H8"/>
       <x:c r="I8" t="str">
-        <x:v>critical facility drone security</x:v>
+        <x:v>metro station drone detector</x:v>
       </x:c>
       <x:c r="J8" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K8" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L8"/>
       <x:c r="M8"/>
@@ -579,13 +579,13 @@
       </x:c>
       <x:c r="H9"/>
       <x:c r="I9" t="str">
-        <x:v>critical asset drone monitoring</x:v>
+        <x:v>bridge c-uas</x:v>
       </x:c>
       <x:c r="J9" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K9" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L9"/>
       <x:c r="M9"/>
@@ -617,13 +617,13 @@
       </x:c>
       <x:c r="H10"/>
       <x:c r="I10" t="str">
-        <x:v>power plant anti drone</x:v>
+        <x:v>nuclear power plant anti drone</x:v>
       </x:c>
       <x:c r="J10" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K10" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L10"/>
       <x:c r="M10"/>
@@ -655,13 +655,13 @@
       </x:c>
       <x:c r="H11"/>
       <x:c r="I11" t="str">
-        <x:v>power plant drone detection</x:v>
+        <x:v>thermal power plant drone detection</x:v>
       </x:c>
       <x:c r="J11" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K11" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L11"/>
       <x:c r="M11"/>
@@ -693,13 +693,13 @@
       </x:c>
       <x:c r="H12"/>
       <x:c r="I12" t="str">
-        <x:v>power plant c-uas</x:v>
+        <x:v>hydroelectric power plant drone detector</x:v>
       </x:c>
       <x:c r="J12" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K12" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L12"/>
       <x:c r="M12"/>
@@ -731,13 +731,13 @@
       </x:c>
       <x:c r="H13"/>
       <x:c r="I13" t="str">
-        <x:v>power plant drone detector</x:v>
+        <x:v>solar farm anti drone</x:v>
       </x:c>
       <x:c r="J13" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K13" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L13"/>
       <x:c r="M13"/>
@@ -769,13 +769,13 @@
       </x:c>
       <x:c r="H14"/>
       <x:c r="I14" t="str">
-        <x:v>power plant airspace monitoring</x:v>
+        <x:v>wind farm drone detection</x:v>
       </x:c>
       <x:c r="J14" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K14" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L14"/>
       <x:c r="M14"/>
@@ -807,13 +807,13 @@
       </x:c>
       <x:c r="H15"/>
       <x:c r="I15" t="str">
-        <x:v>energy facility anti drone</x:v>
+        <x:v>power substation drone detector</x:v>
       </x:c>
       <x:c r="J15" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K15" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L15"/>
       <x:c r="M15"/>
@@ -845,13 +845,13 @@
       </x:c>
       <x:c r="H16"/>
       <x:c r="I16" t="str">
-        <x:v>power grid drone detection</x:v>
+        <x:v>electric grid c-uas</x:v>
       </x:c>
       <x:c r="J16" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K16" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L16"/>
       <x:c r="M16"/>
@@ -883,13 +883,13 @@
       </x:c>
       <x:c r="H17"/>
       <x:c r="I17" t="str">
-        <x:v>substation drone monitoring</x:v>
+        <x:v>power station anti drone</x:v>
       </x:c>
       <x:c r="J17" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K17" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L17"/>
       <x:c r="M17"/>
@@ -927,7 +927,7 @@
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K18" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L18"/>
       <x:c r="M18"/>
@@ -965,7 +965,7 @@
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K19" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L19"/>
       <x:c r="M19"/>
@@ -997,13 +997,13 @@
       </x:c>
       <x:c r="H20"/>
       <x:c r="I20" t="str">
-        <x:v>airport drone detection</x:v>
+        <x:v>runway drone detection</x:v>
       </x:c>
       <x:c r="J20" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K20" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L20"/>
       <x:c r="M20"/>
@@ -1035,13 +1035,13 @@
       </x:c>
       <x:c r="H21"/>
       <x:c r="I21" t="str">
-        <x:v>airport c-uas</x:v>
+        <x:v>airfield drone detector</x:v>
       </x:c>
       <x:c r="J21" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L21"/>
       <x:c r="M21"/>
@@ -1073,13 +1073,13 @@
       </x:c>
       <x:c r="H22"/>
       <x:c r="I22" t="str">
-        <x:v>airport drone detector</x:v>
+        <x:v>airport perimeter anti drone</x:v>
       </x:c>
       <x:c r="J22" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K22" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L22"/>
       <x:c r="M22"/>
@@ -1111,13 +1111,13 @@
       </x:c>
       <x:c r="H23"/>
       <x:c r="I23" t="str">
-        <x:v>airport airspace monitoring</x:v>
+        <x:v>airport c-uas</x:v>
       </x:c>
       <x:c r="J23" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K23" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L23"/>
       <x:c r="M23"/>
@@ -1149,13 +1149,13 @@
       </x:c>
       <x:c r="H24"/>
       <x:c r="I24" t="str">
-        <x:v>runway drone detection</x:v>
+        <x:v>heliport drone detection</x:v>
       </x:c>
       <x:c r="J24" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K24" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L24"/>
       <x:c r="M24"/>
@@ -1187,13 +1187,13 @@
       </x:c>
       <x:c r="H25"/>
       <x:c r="I25" t="str">
-        <x:v>airport counter drone</x:v>
+        <x:v>aviation facility drone security</x:v>
       </x:c>
       <x:c r="J25" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K25" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L25"/>
       <x:c r="M25"/>
@@ -1225,13 +1225,13 @@
       </x:c>
       <x:c r="H26"/>
       <x:c r="I26" t="str">
-        <x:v>border anti drone</x:v>
+        <x:v>border checkpoint anti drone</x:v>
       </x:c>
       <x:c r="J26" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K26" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L26"/>
       <x:c r="M26"/>
@@ -1263,13 +1263,13 @@
       </x:c>
       <x:c r="H27"/>
       <x:c r="I27" t="str">
-        <x:v>border drone detection</x:v>
+        <x:v>border post drone detection</x:v>
       </x:c>
       <x:c r="J27" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K27" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L27"/>
       <x:c r="M27"/>
@@ -1301,13 +1301,13 @@
       </x:c>
       <x:c r="H28"/>
       <x:c r="I28" t="str">
-        <x:v>border c-uas</x:v>
+        <x:v>border patrol c-uas</x:v>
       </x:c>
       <x:c r="J28" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L28"/>
       <x:c r="M28"/>
@@ -1339,13 +1339,13 @@
       </x:c>
       <x:c r="H29"/>
       <x:c r="I29" t="str">
-        <x:v>border drone detector</x:v>
+        <x:v>customs checkpoint drone detector</x:v>
       </x:c>
       <x:c r="J29" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K29" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L29"/>
       <x:c r="M29"/>
@@ -1377,13 +1377,13 @@
       </x:c>
       <x:c r="H30"/>
       <x:c r="I30" t="str">
-        <x:v>border airspace monitoring</x:v>
+        <x:v>land border anti drone</x:v>
       </x:c>
       <x:c r="J30" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K30" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L30"/>
       <x:c r="M30"/>
@@ -1415,13 +1415,13 @@
       </x:c>
       <x:c r="H31"/>
       <x:c r="I31" t="str">
-        <x:v>border counter drone</x:v>
+        <x:v>coastal border drone detection</x:v>
       </x:c>
       <x:c r="J31" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K31" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L31"/>
       <x:c r="M31"/>
@@ -1453,13 +1453,13 @@
       </x:c>
       <x:c r="H32"/>
       <x:c r="I32" t="str">
-        <x:v>border patrol drone detection</x:v>
+        <x:v>remote border post drone security</x:v>
       </x:c>
       <x:c r="J32" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K32" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L32"/>
       <x:c r="M32"/>
@@ -1491,13 +1491,13 @@
       </x:c>
       <x:c r="H33"/>
       <x:c r="I33" t="str">
-        <x:v>frontier drone monitoring</x:v>
+        <x:v>frontier drone detector</x:v>
       </x:c>
       <x:c r="J33" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K33" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L33"/>
       <x:c r="M33"/>
@@ -1529,13 +1529,13 @@
       </x:c>
       <x:c r="H34"/>
       <x:c r="I34" t="str">
-        <x:v>public safety anti drone</x:v>
+        <x:v>police station anti drone</x:v>
       </x:c>
       <x:c r="J34" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K34" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L34"/>
       <x:c r="M34"/>
@@ -1567,13 +1567,13 @@
       </x:c>
       <x:c r="H35"/>
       <x:c r="I35" t="str">
-        <x:v>public safety drone detection</x:v>
+        <x:v>law enforcement drone detection</x:v>
       </x:c>
       <x:c r="J35" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K35" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L35"/>
       <x:c r="M35"/>
@@ -1605,13 +1605,13 @@
       </x:c>
       <x:c r="H36"/>
       <x:c r="I36" t="str">
-        <x:v>public safety c-uas</x:v>
+        <x:v>emergency command center anti drone</x:v>
       </x:c>
       <x:c r="J36" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K36" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L36"/>
       <x:c r="M36"/>
@@ -1643,13 +1643,13 @@
       </x:c>
       <x:c r="H37"/>
       <x:c r="I37" t="str">
-        <x:v>public safety drone detector</x:v>
+        <x:v>city center drone detector</x:v>
       </x:c>
       <x:c r="J37" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K37" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L37"/>
       <x:c r="M37"/>
@@ -1681,13 +1681,13 @@
       </x:c>
       <x:c r="H38"/>
       <x:c r="I38" t="str">
-        <x:v>law enforcement anti drone</x:v>
+        <x:v>urban security c-uas</x:v>
       </x:c>
       <x:c r="J38" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K38" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L38"/>
       <x:c r="M38"/>
@@ -1719,13 +1719,13 @@
       </x:c>
       <x:c r="H39"/>
       <x:c r="I39" t="str">
-        <x:v>police drone detection</x:v>
+        <x:v>public square drone detection</x:v>
       </x:c>
       <x:c r="J39" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K39" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L39"/>
       <x:c r="M39"/>
@@ -1757,13 +1757,13 @@
       </x:c>
       <x:c r="H40"/>
       <x:c r="I40" t="str">
-        <x:v>emergency response drone monitoring</x:v>
+        <x:v>fire department anti drone</x:v>
       </x:c>
       <x:c r="J40" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K40" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L40"/>
       <x:c r="M40"/>
@@ -1795,13 +1795,13 @@
       </x:c>
       <x:c r="H41"/>
       <x:c r="I41" t="str">
-        <x:v>urban drone security</x:v>
+        <x:v>emergency response drone security</x:v>
       </x:c>
       <x:c r="J41" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K41" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L41"/>
       <x:c r="M41"/>
@@ -1839,7 +1839,7 @@
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K42" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L42"/>
       <x:c r="M42"/>
@@ -1871,13 +1871,13 @@
       </x:c>
       <x:c r="H43"/>
       <x:c r="I43" t="str">
-        <x:v>prison drone detection</x:v>
+        <x:v>correctional facility drone detection</x:v>
       </x:c>
       <x:c r="J43" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K43" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L43"/>
       <x:c r="M43"/>
@@ -1909,13 +1909,13 @@
       </x:c>
       <x:c r="H44"/>
       <x:c r="I44" t="str">
-        <x:v>prison c-uas</x:v>
+        <x:v>jail drone detector</x:v>
       </x:c>
       <x:c r="J44" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K44" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L44"/>
       <x:c r="M44"/>
@@ -1947,13 +1947,13 @@
       </x:c>
       <x:c r="H45"/>
       <x:c r="I45" t="str">
-        <x:v>prison drone detector</x:v>
+        <x:v>detention center anti drone</x:v>
       </x:c>
       <x:c r="J45" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K45" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L45"/>
       <x:c r="M45"/>
@@ -1985,13 +1985,13 @@
       </x:c>
       <x:c r="H46"/>
       <x:c r="I46" t="str">
-        <x:v>prison drone monitoring</x:v>
+        <x:v>prison perimeter c-uas</x:v>
       </x:c>
       <x:c r="J46" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K46" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L46"/>
       <x:c r="M46"/>
@@ -2023,13 +2023,13 @@
       </x:c>
       <x:c r="H47"/>
       <x:c r="I47" t="str">
-        <x:v>correctional facility anti drone</x:v>
+        <x:v>prison contraband drone detection</x:v>
       </x:c>
       <x:c r="J47" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K47" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L47"/>
       <x:c r="M47"/>
@@ -2061,13 +2061,13 @@
       </x:c>
       <x:c r="H48"/>
       <x:c r="I48" t="str">
-        <x:v>contraband drone detection</x:v>
+        <x:v>penitentiary drone security</x:v>
       </x:c>
       <x:c r="J48" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K48" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L48"/>
       <x:c r="M48"/>
@@ -2099,13 +2099,13 @@
       </x:c>
       <x:c r="H49"/>
       <x:c r="I49" t="str">
-        <x:v>prison perimeter drone security</x:v>
+        <x:v>prison drone locator</x:v>
       </x:c>
       <x:c r="J49" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K49" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L49"/>
       <x:c r="M49"/>
@@ -2137,13 +2137,13 @@
       </x:c>
       <x:c r="H50"/>
       <x:c r="I50" t="str">
-        <x:v>port anti drone</x:v>
+        <x:v>seaport anti drone</x:v>
       </x:c>
       <x:c r="J50" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K50" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L50"/>
       <x:c r="M50"/>
@@ -2175,13 +2175,13 @@
       </x:c>
       <x:c r="H51"/>
       <x:c r="I51" t="str">
-        <x:v>port drone detection</x:v>
+        <x:v>harbor drone detection</x:v>
       </x:c>
       <x:c r="J51" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K51" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L51"/>
       <x:c r="M51"/>
@@ -2213,13 +2213,13 @@
       </x:c>
       <x:c r="H52"/>
       <x:c r="I52" t="str">
-        <x:v>port c-uas</x:v>
+        <x:v>container terminal drone detector</x:v>
       </x:c>
       <x:c r="J52" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K52" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L52"/>
       <x:c r="M52"/>
@@ -2251,13 +2251,13 @@
       </x:c>
       <x:c r="H53"/>
       <x:c r="I53" t="str">
-        <x:v>port drone detector</x:v>
+        <x:v>cargo terminal anti drone</x:v>
       </x:c>
       <x:c r="J53" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K53" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L53"/>
       <x:c r="M53"/>
@@ -2289,13 +2289,13 @@
       </x:c>
       <x:c r="H54"/>
       <x:c r="I54" t="str">
-        <x:v>port airspace monitoring</x:v>
+        <x:v>oil port drone detection</x:v>
       </x:c>
       <x:c r="J54" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K54" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L54"/>
       <x:c r="M54"/>
@@ -2327,13 +2327,13 @@
       </x:c>
       <x:c r="H55"/>
       <x:c r="I55" t="str">
-        <x:v>seaport anti drone</x:v>
+        <x:v>port warehouse drone security</x:v>
       </x:c>
       <x:c r="J55" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K55" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L55"/>
       <x:c r="M55"/>
@@ -2365,13 +2365,13 @@
       </x:c>
       <x:c r="H56"/>
       <x:c r="I56" t="str">
-        <x:v>harbor drone detection</x:v>
+        <x:v>port c-uas</x:v>
       </x:c>
       <x:c r="J56" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K56" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L56"/>
       <x:c r="M56"/>
@@ -2403,13 +2403,13 @@
       </x:c>
       <x:c r="H57"/>
       <x:c r="I57" t="str">
-        <x:v>port security drone monitoring</x:v>
+        <x:v>shipping terminal drone detection</x:v>
       </x:c>
       <x:c r="J57" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K57" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L57"/>
       <x:c r="M57"/>
@@ -2441,13 +2441,13 @@
       </x:c>
       <x:c r="H58"/>
       <x:c r="I58" t="str">
-        <x:v>mass event anti drone</x:v>
+        <x:v>stadium anti drone</x:v>
       </x:c>
       <x:c r="J58" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K58" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L58"/>
       <x:c r="M58"/>
@@ -2479,13 +2479,13 @@
       </x:c>
       <x:c r="H59"/>
       <x:c r="I59" t="str">
-        <x:v>mass event drone detection</x:v>
+        <x:v>football stadium drone detection</x:v>
       </x:c>
       <x:c r="J59" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K59" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L59"/>
       <x:c r="M59"/>
@@ -2517,13 +2517,13 @@
       </x:c>
       <x:c r="H60"/>
       <x:c r="I60" t="str">
-        <x:v>mass event c-uas</x:v>
+        <x:v>sports event c-uas</x:v>
       </x:c>
       <x:c r="J60" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K60" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L60"/>
       <x:c r="M60"/>
@@ -2555,13 +2555,13 @@
       </x:c>
       <x:c r="H61"/>
       <x:c r="I61" t="str">
-        <x:v>stadium anti drone</x:v>
+        <x:v>concert drone detector</x:v>
       </x:c>
       <x:c r="J61" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K61" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L61"/>
       <x:c r="M61"/>
@@ -2593,13 +2593,13 @@
       </x:c>
       <x:c r="H62"/>
       <x:c r="I62" t="str">
-        <x:v>stadium drone detection</x:v>
+        <x:v>music festival anti drone</x:v>
       </x:c>
       <x:c r="J62" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K62" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L62"/>
       <x:c r="M62"/>
@@ -2631,13 +2631,13 @@
       </x:c>
       <x:c r="H63"/>
       <x:c r="I63" t="str">
-        <x:v>sports event drone security</x:v>
+        <x:v>convention center drone detection</x:v>
       </x:c>
       <x:c r="J63" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K63" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L63"/>
       <x:c r="M63"/>
@@ -2669,13 +2669,13 @@
       </x:c>
       <x:c r="H64"/>
       <x:c r="I64" t="str">
-        <x:v>concert drone detection</x:v>
+        <x:v>exhibition center anti drone</x:v>
       </x:c>
       <x:c r="J64" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K64" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L64"/>
       <x:c r="M64"/>
@@ -2707,13 +2707,13 @@
       </x:c>
       <x:c r="H65"/>
       <x:c r="I65" t="str">
-        <x:v>crowded event drone detection</x:v>
+        <x:v>large event drone security</x:v>
       </x:c>
       <x:c r="J65" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K65" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L65"/>
       <x:c r="M65"/>
@@ -2745,13 +2745,13 @@
       </x:c>
       <x:c r="H66"/>
       <x:c r="I66" t="str">
-        <x:v>vip anti drone</x:v>
+        <x:v>villa anti drone</x:v>
       </x:c>
       <x:c r="J66" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K66" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L66"/>
       <x:c r="M66"/>
@@ -2783,13 +2783,13 @@
       </x:c>
       <x:c r="H67"/>
       <x:c r="I67" t="str">
-        <x:v>vip drone detection</x:v>
+        <x:v>luxury villa drone detection</x:v>
       </x:c>
       <x:c r="J67" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K67" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L67"/>
       <x:c r="M67"/>
@@ -2821,13 +2821,13 @@
       </x:c>
       <x:c r="H68"/>
       <x:c r="I68" t="str">
-        <x:v>vip c-uas</x:v>
+        <x:v>private estate drone detector</x:v>
       </x:c>
       <x:c r="J68" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K68" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L68"/>
       <x:c r="M68"/>
@@ -2859,13 +2859,13 @@
       </x:c>
       <x:c r="H69"/>
       <x:c r="I69" t="str">
-        <x:v>vip drone detector</x:v>
+        <x:v>mansion anti drone</x:v>
       </x:c>
       <x:c r="J69" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K69" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L69"/>
       <x:c r="M69"/>
@@ -2897,13 +2897,13 @@
       </x:c>
       <x:c r="H70"/>
       <x:c r="I70" t="str">
-        <x:v>private property anti drone</x:v>
+        <x:v>private residence c-uas</x:v>
       </x:c>
       <x:c r="J70" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K70" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L70"/>
       <x:c r="M70"/>
@@ -2935,13 +2935,13 @@
       </x:c>
       <x:c r="H71"/>
       <x:c r="I71" t="str">
-        <x:v>private property drone detection</x:v>
+        <x:v>vip convoy drone security</x:v>
       </x:c>
       <x:c r="J71" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K71" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L71"/>
       <x:c r="M71"/>
@@ -2973,13 +2973,13 @@
       </x:c>
       <x:c r="H72"/>
       <x:c r="I72" t="str">
-        <x:v>vip convoy drone security</x:v>
+        <x:v>yacht anti drone</x:v>
       </x:c>
       <x:c r="J72" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K72" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L72"/>
       <x:c r="M72"/>
@@ -3011,13 +3011,13 @@
       </x:c>
       <x:c r="H73"/>
       <x:c r="I73" t="str">
-        <x:v>private estate drone detection</x:v>
+        <x:v>private ranch drone detection</x:v>
       </x:c>
       <x:c r="J73" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K73" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L73"/>
       <x:c r="M73"/>
@@ -3049,13 +3049,13 @@
       </x:c>
       <x:c r="H74"/>
       <x:c r="I74" t="str">
-        <x:v>enterprise anti drone</x:v>
+        <x:v>mine anti drone</x:v>
       </x:c>
       <x:c r="J74" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K74" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L74"/>
       <x:c r="M74"/>
@@ -3087,13 +3087,13 @@
       </x:c>
       <x:c r="H75"/>
       <x:c r="I75" t="str">
-        <x:v>enterprise drone detection</x:v>
+        <x:v>mining site drone detection</x:v>
       </x:c>
       <x:c r="J75" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K75" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L75"/>
       <x:c r="M75"/>
@@ -3125,13 +3125,13 @@
       </x:c>
       <x:c r="H76"/>
       <x:c r="I76" t="str">
-        <x:v>enterprise c-uas</x:v>
+        <x:v>oil refinery anti drone</x:v>
       </x:c>
       <x:c r="J76" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K76" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L76"/>
       <x:c r="M76"/>
@@ -3163,13 +3163,13 @@
       </x:c>
       <x:c r="H77"/>
       <x:c r="I77" t="str">
-        <x:v>enterprise drone detector</x:v>
+        <x:v>oil field drone detector</x:v>
       </x:c>
       <x:c r="J77" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K77" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L77"/>
       <x:c r="M77"/>
@@ -3201,13 +3201,13 @@
       </x:c>
       <x:c r="H78"/>
       <x:c r="I78" t="str">
-        <x:v>corporate headquarters anti drone</x:v>
+        <x:v>factory drone detection</x:v>
       </x:c>
       <x:c r="J78" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K78" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L78"/>
       <x:c r="M78"/>
@@ -3239,13 +3239,13 @@
       </x:c>
       <x:c r="H79"/>
       <x:c r="I79" t="str">
-        <x:v>corporate campus drone detection</x:v>
+        <x:v>industrial park c-uas</x:v>
       </x:c>
       <x:c r="J79" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K79" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L79"/>
       <x:c r="M79"/>
@@ -3277,13 +3277,13 @@
       </x:c>
       <x:c r="H80"/>
       <x:c r="I80" t="str">
-        <x:v>business campus drone security</x:v>
+        <x:v>corporate headquarters anti drone</x:v>
       </x:c>
       <x:c r="J80" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K80" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L80"/>
       <x:c r="M80"/>
@@ -3315,13 +3315,13 @@
       </x:c>
       <x:c r="H81"/>
       <x:c r="I81" t="str">
-        <x:v>enterprise airspace monitoring</x:v>
+        <x:v>warehouse drone security</x:v>
       </x:c>
       <x:c r="J81" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K81" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L81"/>
       <x:c r="M81"/>
@@ -3353,13 +3353,13 @@
       </x:c>
       <x:c r="H82"/>
       <x:c r="I82" t="str">
-        <x:v>critical infrastructure anti drone</x:v>
+        <x:v>government building anti drone</x:v>
       </x:c>
       <x:c r="J82" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K82" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L82"/>
       <x:c r="M82"/>
@@ -3391,13 +3391,13 @@
       </x:c>
       <x:c r="H83"/>
       <x:c r="I83" t="str">
-        <x:v>critical infrastructure drone detection</x:v>
+        <x:v>data center drone detection</x:v>
       </x:c>
       <x:c r="J83" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K83" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L83"/>
       <x:c r="M83"/>
@@ -3429,13 +3429,13 @@
       </x:c>
       <x:c r="H84"/>
       <x:c r="I84" t="str">
-        <x:v>critical infrastructure c-uas</x:v>
+        <x:v>telecom tower drone detector</x:v>
       </x:c>
       <x:c r="J84" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K84" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L84"/>
       <x:c r="M84"/>
@@ -3467,13 +3467,13 @@
       </x:c>
       <x:c r="H85"/>
       <x:c r="I85" t="str">
-        <x:v>critical infrastructure drone detector</x:v>
+        <x:v>water treatment plant anti drone</x:v>
       </x:c>
       <x:c r="J85" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K85" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L85"/>
       <x:c r="M85"/>
@@ -3505,13 +3505,13 @@
       </x:c>
       <x:c r="H86"/>
       <x:c r="I86" t="str">
-        <x:v>critical infrastructure airspace monitoring</x:v>
+        <x:v>dam drone detection</x:v>
       </x:c>
       <x:c r="J86" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K86" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L86"/>
       <x:c r="M86"/>
@@ -3543,13 +3543,13 @@
       </x:c>
       <x:c r="H87"/>
       <x:c r="I87" t="str">
-        <x:v>critical infrastructure counter drone</x:v>
+        <x:v>railway station anti drone</x:v>
       </x:c>
       <x:c r="J87" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K87" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L87"/>
       <x:c r="M87"/>
@@ -3581,13 +3581,13 @@
       </x:c>
       <x:c r="H88"/>
       <x:c r="I88" t="str">
-        <x:v>critical facility drone security</x:v>
+        <x:v>metro station drone detector</x:v>
       </x:c>
       <x:c r="J88" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K88" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L88"/>
       <x:c r="M88"/>
@@ -3619,13 +3619,13 @@
       </x:c>
       <x:c r="H89"/>
       <x:c r="I89" t="str">
-        <x:v>critical asset drone monitoring</x:v>
+        <x:v>bridge c-uas</x:v>
       </x:c>
       <x:c r="J89" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K89" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L89"/>
       <x:c r="M89"/>
@@ -3657,13 +3657,13 @@
       </x:c>
       <x:c r="H90"/>
       <x:c r="I90" t="str">
-        <x:v>power plant anti drone</x:v>
+        <x:v>nuclear power plant anti drone</x:v>
       </x:c>
       <x:c r="J90" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K90" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L90"/>
       <x:c r="M90"/>
@@ -3695,13 +3695,13 @@
       </x:c>
       <x:c r="H91"/>
       <x:c r="I91" t="str">
-        <x:v>power plant drone detection</x:v>
+        <x:v>thermal power plant drone detection</x:v>
       </x:c>
       <x:c r="J91" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K91" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L91"/>
       <x:c r="M91"/>
@@ -3733,13 +3733,13 @@
       </x:c>
       <x:c r="H92"/>
       <x:c r="I92" t="str">
-        <x:v>power plant c-uas</x:v>
+        <x:v>hydroelectric power plant drone detector</x:v>
       </x:c>
       <x:c r="J92" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K92" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L92"/>
       <x:c r="M92"/>
@@ -3771,13 +3771,13 @@
       </x:c>
       <x:c r="H93"/>
       <x:c r="I93" t="str">
-        <x:v>power plant drone detector</x:v>
+        <x:v>solar farm anti drone</x:v>
       </x:c>
       <x:c r="J93" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K93" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L93"/>
       <x:c r="M93"/>
@@ -3809,13 +3809,13 @@
       </x:c>
       <x:c r="H94"/>
       <x:c r="I94" t="str">
-        <x:v>power plant airspace monitoring</x:v>
+        <x:v>wind farm drone detection</x:v>
       </x:c>
       <x:c r="J94" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K94" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L94"/>
       <x:c r="M94"/>
@@ -3847,13 +3847,13 @@
       </x:c>
       <x:c r="H95"/>
       <x:c r="I95" t="str">
-        <x:v>energy facility anti drone</x:v>
+        <x:v>power substation drone detector</x:v>
       </x:c>
       <x:c r="J95" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K95" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L95"/>
       <x:c r="M95"/>
@@ -3885,13 +3885,13 @@
       </x:c>
       <x:c r="H96"/>
       <x:c r="I96" t="str">
-        <x:v>power grid drone detection</x:v>
+        <x:v>electric grid c-uas</x:v>
       </x:c>
       <x:c r="J96" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K96" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L96"/>
       <x:c r="M96"/>
@@ -3923,13 +3923,13 @@
       </x:c>
       <x:c r="H97"/>
       <x:c r="I97" t="str">
-        <x:v>substation drone monitoring</x:v>
+        <x:v>power station anti drone</x:v>
       </x:c>
       <x:c r="J97" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K97" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L97"/>
       <x:c r="M97"/>
@@ -3967,7 +3967,7 @@
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K98" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L98"/>
       <x:c r="M98"/>
@@ -4005,7 +4005,7 @@
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K99" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L99"/>
       <x:c r="M99"/>
@@ -4037,13 +4037,13 @@
       </x:c>
       <x:c r="H100"/>
       <x:c r="I100" t="str">
-        <x:v>airport drone detection</x:v>
+        <x:v>runway drone detection</x:v>
       </x:c>
       <x:c r="J100" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K100" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L100"/>
       <x:c r="M100"/>
@@ -4075,13 +4075,13 @@
       </x:c>
       <x:c r="H101"/>
       <x:c r="I101" t="str">
-        <x:v>airport c-uas</x:v>
+        <x:v>airfield drone detector</x:v>
       </x:c>
       <x:c r="J101" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K101" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L101"/>
       <x:c r="M101"/>
@@ -4113,13 +4113,13 @@
       </x:c>
       <x:c r="H102"/>
       <x:c r="I102" t="str">
-        <x:v>airport drone detector</x:v>
+        <x:v>airport perimeter anti drone</x:v>
       </x:c>
       <x:c r="J102" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K102" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L102"/>
       <x:c r="M102"/>
@@ -4151,13 +4151,13 @@
       </x:c>
       <x:c r="H103"/>
       <x:c r="I103" t="str">
-        <x:v>airport airspace monitoring</x:v>
+        <x:v>airport c-uas</x:v>
       </x:c>
       <x:c r="J103" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K103" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L103"/>
       <x:c r="M103"/>
@@ -4189,13 +4189,13 @@
       </x:c>
       <x:c r="H104"/>
       <x:c r="I104" t="str">
-        <x:v>runway drone detection</x:v>
+        <x:v>heliport drone detection</x:v>
       </x:c>
       <x:c r="J104" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K104" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L104"/>
       <x:c r="M104"/>
@@ -4227,13 +4227,13 @@
       </x:c>
       <x:c r="H105"/>
       <x:c r="I105" t="str">
-        <x:v>airport counter drone</x:v>
+        <x:v>aviation facility drone security</x:v>
       </x:c>
       <x:c r="J105" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K105" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L105"/>
       <x:c r="M105"/>
@@ -4265,13 +4265,13 @@
       </x:c>
       <x:c r="H106"/>
       <x:c r="I106" t="str">
-        <x:v>border anti drone</x:v>
+        <x:v>border checkpoint anti drone</x:v>
       </x:c>
       <x:c r="J106" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K106" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L106"/>
       <x:c r="M106"/>
@@ -4303,13 +4303,13 @@
       </x:c>
       <x:c r="H107"/>
       <x:c r="I107" t="str">
-        <x:v>border drone detection</x:v>
+        <x:v>border post drone detection</x:v>
       </x:c>
       <x:c r="J107" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K107" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L107"/>
       <x:c r="M107"/>
@@ -4341,13 +4341,13 @@
       </x:c>
       <x:c r="H108"/>
       <x:c r="I108" t="str">
-        <x:v>border c-uas</x:v>
+        <x:v>border patrol c-uas</x:v>
       </x:c>
       <x:c r="J108" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K108" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L108"/>
       <x:c r="M108"/>
@@ -4379,13 +4379,13 @@
       </x:c>
       <x:c r="H109"/>
       <x:c r="I109" t="str">
-        <x:v>border drone detector</x:v>
+        <x:v>customs checkpoint drone detector</x:v>
       </x:c>
       <x:c r="J109" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K109" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L109"/>
       <x:c r="M109"/>
@@ -4417,13 +4417,13 @@
       </x:c>
       <x:c r="H110"/>
       <x:c r="I110" t="str">
-        <x:v>border airspace monitoring</x:v>
+        <x:v>land border anti drone</x:v>
       </x:c>
       <x:c r="J110" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K110" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L110"/>
       <x:c r="M110"/>
@@ -4455,13 +4455,13 @@
       </x:c>
       <x:c r="H111"/>
       <x:c r="I111" t="str">
-        <x:v>border counter drone</x:v>
+        <x:v>coastal border drone detection</x:v>
       </x:c>
       <x:c r="J111" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K111" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L111"/>
       <x:c r="M111"/>
@@ -4493,13 +4493,13 @@
       </x:c>
       <x:c r="H112"/>
       <x:c r="I112" t="str">
-        <x:v>border patrol drone detection</x:v>
+        <x:v>remote border post drone security</x:v>
       </x:c>
       <x:c r="J112" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K112" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L112"/>
       <x:c r="M112"/>
@@ -4531,13 +4531,13 @@
       </x:c>
       <x:c r="H113"/>
       <x:c r="I113" t="str">
-        <x:v>frontier drone monitoring</x:v>
+        <x:v>frontier drone detector</x:v>
       </x:c>
       <x:c r="J113" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K113" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L113"/>
       <x:c r="M113"/>
@@ -4569,13 +4569,13 @@
       </x:c>
       <x:c r="H114"/>
       <x:c r="I114" t="str">
-        <x:v>public safety anti drone</x:v>
+        <x:v>police station anti drone</x:v>
       </x:c>
       <x:c r="J114" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K114" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L114"/>
       <x:c r="M114"/>
@@ -4607,13 +4607,13 @@
       </x:c>
       <x:c r="H115"/>
       <x:c r="I115" t="str">
-        <x:v>public safety drone detection</x:v>
+        <x:v>law enforcement drone detection</x:v>
       </x:c>
       <x:c r="J115" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K115" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L115"/>
       <x:c r="M115"/>
@@ -4645,13 +4645,13 @@
       </x:c>
       <x:c r="H116"/>
       <x:c r="I116" t="str">
-        <x:v>public safety c-uas</x:v>
+        <x:v>emergency command center anti drone</x:v>
       </x:c>
       <x:c r="J116" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K116" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L116"/>
       <x:c r="M116"/>
@@ -4683,13 +4683,13 @@
       </x:c>
       <x:c r="H117"/>
       <x:c r="I117" t="str">
-        <x:v>public safety drone detector</x:v>
+        <x:v>city center drone detector</x:v>
       </x:c>
       <x:c r="J117" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K117" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L117"/>
       <x:c r="M117"/>
@@ -4721,13 +4721,13 @@
       </x:c>
       <x:c r="H118"/>
       <x:c r="I118" t="str">
-        <x:v>law enforcement anti drone</x:v>
+        <x:v>urban security c-uas</x:v>
       </x:c>
       <x:c r="J118" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K118" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L118"/>
       <x:c r="M118"/>
@@ -4759,13 +4759,13 @@
       </x:c>
       <x:c r="H119"/>
       <x:c r="I119" t="str">
-        <x:v>police drone detection</x:v>
+        <x:v>public square drone detection</x:v>
       </x:c>
       <x:c r="J119" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K119" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L119"/>
       <x:c r="M119"/>
@@ -4797,13 +4797,13 @@
       </x:c>
       <x:c r="H120"/>
       <x:c r="I120" t="str">
-        <x:v>emergency response drone monitoring</x:v>
+        <x:v>fire department anti drone</x:v>
       </x:c>
       <x:c r="J120" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K120" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L120"/>
       <x:c r="M120"/>
@@ -4835,13 +4835,13 @@
       </x:c>
       <x:c r="H121"/>
       <x:c r="I121" t="str">
-        <x:v>urban drone security</x:v>
+        <x:v>emergency response drone security</x:v>
       </x:c>
       <x:c r="J121" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K121" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L121"/>
       <x:c r="M121"/>
@@ -4879,7 +4879,7 @@
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K122" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L122"/>
       <x:c r="M122"/>
@@ -4911,13 +4911,13 @@
       </x:c>
       <x:c r="H123"/>
       <x:c r="I123" t="str">
-        <x:v>prison drone detection</x:v>
+        <x:v>correctional facility drone detection</x:v>
       </x:c>
       <x:c r="J123" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K123" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L123"/>
       <x:c r="M123"/>
@@ -4949,13 +4949,13 @@
       </x:c>
       <x:c r="H124"/>
       <x:c r="I124" t="str">
-        <x:v>prison c-uas</x:v>
+        <x:v>jail drone detector</x:v>
       </x:c>
       <x:c r="J124" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K124" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L124"/>
       <x:c r="M124"/>
@@ -4987,13 +4987,13 @@
       </x:c>
       <x:c r="H125"/>
       <x:c r="I125" t="str">
-        <x:v>prison drone detector</x:v>
+        <x:v>detention center anti drone</x:v>
       </x:c>
       <x:c r="J125" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K125" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L125"/>
       <x:c r="M125"/>
@@ -5025,13 +5025,13 @@
       </x:c>
       <x:c r="H126"/>
       <x:c r="I126" t="str">
-        <x:v>prison drone monitoring</x:v>
+        <x:v>prison perimeter c-uas</x:v>
       </x:c>
       <x:c r="J126" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K126" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L126"/>
       <x:c r="M126"/>
@@ -5063,13 +5063,13 @@
       </x:c>
       <x:c r="H127"/>
       <x:c r="I127" t="str">
-        <x:v>correctional facility anti drone</x:v>
+        <x:v>prison contraband drone detection</x:v>
       </x:c>
       <x:c r="J127" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K127" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L127"/>
       <x:c r="M127"/>
@@ -5101,13 +5101,13 @@
       </x:c>
       <x:c r="H128"/>
       <x:c r="I128" t="str">
-        <x:v>contraband drone detection</x:v>
+        <x:v>penitentiary drone security</x:v>
       </x:c>
       <x:c r="J128" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K128" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L128"/>
       <x:c r="M128"/>
@@ -5139,13 +5139,13 @@
       </x:c>
       <x:c r="H129"/>
       <x:c r="I129" t="str">
-        <x:v>prison perimeter drone security</x:v>
+        <x:v>prison drone locator</x:v>
       </x:c>
       <x:c r="J129" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K129" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L129"/>
       <x:c r="M129"/>
@@ -5177,13 +5177,13 @@
       </x:c>
       <x:c r="H130"/>
       <x:c r="I130" t="str">
-        <x:v>port anti drone</x:v>
+        <x:v>seaport anti drone</x:v>
       </x:c>
       <x:c r="J130" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K130" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L130"/>
       <x:c r="M130"/>
@@ -5215,13 +5215,13 @@
       </x:c>
       <x:c r="H131"/>
       <x:c r="I131" t="str">
-        <x:v>port drone detection</x:v>
+        <x:v>harbor drone detection</x:v>
       </x:c>
       <x:c r="J131" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K131" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L131"/>
       <x:c r="M131"/>
@@ -5253,13 +5253,13 @@
       </x:c>
       <x:c r="H132"/>
       <x:c r="I132" t="str">
-        <x:v>port c-uas</x:v>
+        <x:v>container terminal drone detector</x:v>
       </x:c>
       <x:c r="J132" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K132" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L132"/>
       <x:c r="M132"/>
@@ -5291,13 +5291,13 @@
       </x:c>
       <x:c r="H133"/>
       <x:c r="I133" t="str">
-        <x:v>port drone detector</x:v>
+        <x:v>cargo terminal anti drone</x:v>
       </x:c>
       <x:c r="J133" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K133" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L133"/>
       <x:c r="M133"/>
@@ -5329,13 +5329,13 @@
       </x:c>
       <x:c r="H134"/>
       <x:c r="I134" t="str">
-        <x:v>port airspace monitoring</x:v>
+        <x:v>oil port drone detection</x:v>
       </x:c>
       <x:c r="J134" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K134" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L134"/>
       <x:c r="M134"/>
@@ -5367,13 +5367,13 @@
       </x:c>
       <x:c r="H135"/>
       <x:c r="I135" t="str">
-        <x:v>seaport anti drone</x:v>
+        <x:v>port warehouse drone security</x:v>
       </x:c>
       <x:c r="J135" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K135" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L135"/>
       <x:c r="M135"/>
@@ -5405,13 +5405,13 @@
       </x:c>
       <x:c r="H136"/>
       <x:c r="I136" t="str">
-        <x:v>harbor drone detection</x:v>
+        <x:v>port c-uas</x:v>
       </x:c>
       <x:c r="J136" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K136" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L136"/>
       <x:c r="M136"/>
@@ -5443,13 +5443,13 @@
       </x:c>
       <x:c r="H137"/>
       <x:c r="I137" t="str">
-        <x:v>port security drone monitoring</x:v>
+        <x:v>shipping terminal drone detection</x:v>
       </x:c>
       <x:c r="J137" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K137" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L137"/>
       <x:c r="M137"/>
@@ -5481,13 +5481,13 @@
       </x:c>
       <x:c r="H138"/>
       <x:c r="I138" t="str">
-        <x:v>mass event anti drone</x:v>
+        <x:v>stadium anti drone</x:v>
       </x:c>
       <x:c r="J138" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K138" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L138"/>
       <x:c r="M138"/>
@@ -5519,13 +5519,13 @@
       </x:c>
       <x:c r="H139"/>
       <x:c r="I139" t="str">
-        <x:v>mass event drone detection</x:v>
+        <x:v>football stadium drone detection</x:v>
       </x:c>
       <x:c r="J139" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K139" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L139"/>
       <x:c r="M139"/>
@@ -5557,13 +5557,13 @@
       </x:c>
       <x:c r="H140"/>
       <x:c r="I140" t="str">
-        <x:v>mass event c-uas</x:v>
+        <x:v>sports event c-uas</x:v>
       </x:c>
       <x:c r="J140" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K140" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L140"/>
       <x:c r="M140"/>
@@ -5595,13 +5595,13 @@
       </x:c>
       <x:c r="H141"/>
       <x:c r="I141" t="str">
-        <x:v>stadium anti drone</x:v>
+        <x:v>concert drone detector</x:v>
       </x:c>
       <x:c r="J141" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K141" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L141"/>
       <x:c r="M141"/>
@@ -5633,13 +5633,13 @@
       </x:c>
       <x:c r="H142"/>
       <x:c r="I142" t="str">
-        <x:v>stadium drone detection</x:v>
+        <x:v>music festival anti drone</x:v>
       </x:c>
       <x:c r="J142" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K142" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L142"/>
       <x:c r="M142"/>
@@ -5671,13 +5671,13 @@
       </x:c>
       <x:c r="H143"/>
       <x:c r="I143" t="str">
-        <x:v>sports event drone security</x:v>
+        <x:v>convention center drone detection</x:v>
       </x:c>
       <x:c r="J143" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K143" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L143"/>
       <x:c r="M143"/>
@@ -5709,13 +5709,13 @@
       </x:c>
       <x:c r="H144"/>
       <x:c r="I144" t="str">
-        <x:v>concert drone detection</x:v>
+        <x:v>exhibition center anti drone</x:v>
       </x:c>
       <x:c r="J144" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K144" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L144"/>
       <x:c r="M144"/>
@@ -5747,13 +5747,13 @@
       </x:c>
       <x:c r="H145"/>
       <x:c r="I145" t="str">
-        <x:v>crowded event drone detection</x:v>
+        <x:v>large event drone security</x:v>
       </x:c>
       <x:c r="J145" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K145" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L145"/>
       <x:c r="M145"/>
@@ -5785,13 +5785,13 @@
       </x:c>
       <x:c r="H146"/>
       <x:c r="I146" t="str">
-        <x:v>vip anti drone</x:v>
+        <x:v>villa anti drone</x:v>
       </x:c>
       <x:c r="J146" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K146" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L146"/>
       <x:c r="M146"/>
@@ -5823,13 +5823,13 @@
       </x:c>
       <x:c r="H147"/>
       <x:c r="I147" t="str">
-        <x:v>vip drone detection</x:v>
+        <x:v>luxury villa drone detection</x:v>
       </x:c>
       <x:c r="J147" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K147" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L147"/>
       <x:c r="M147"/>
@@ -5861,13 +5861,13 @@
       </x:c>
       <x:c r="H148"/>
       <x:c r="I148" t="str">
-        <x:v>vip c-uas</x:v>
+        <x:v>private estate drone detector</x:v>
       </x:c>
       <x:c r="J148" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K148" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L148"/>
       <x:c r="M148"/>
@@ -5899,13 +5899,13 @@
       </x:c>
       <x:c r="H149"/>
       <x:c r="I149" t="str">
-        <x:v>vip drone detector</x:v>
+        <x:v>mansion anti drone</x:v>
       </x:c>
       <x:c r="J149" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K149" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L149"/>
       <x:c r="M149"/>
@@ -5937,13 +5937,13 @@
       </x:c>
       <x:c r="H150"/>
       <x:c r="I150" t="str">
-        <x:v>private property anti drone</x:v>
+        <x:v>private residence c-uas</x:v>
       </x:c>
       <x:c r="J150" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K150" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L150"/>
       <x:c r="M150"/>
@@ -5975,13 +5975,13 @@
       </x:c>
       <x:c r="H151"/>
       <x:c r="I151" t="str">
-        <x:v>private property drone detection</x:v>
+        <x:v>vip convoy drone security</x:v>
       </x:c>
       <x:c r="J151" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K151" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L151"/>
       <x:c r="M151"/>
@@ -6013,13 +6013,13 @@
       </x:c>
       <x:c r="H152"/>
       <x:c r="I152" t="str">
-        <x:v>vip convoy drone security</x:v>
+        <x:v>yacht anti drone</x:v>
       </x:c>
       <x:c r="J152" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K152" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L152"/>
       <x:c r="M152"/>
@@ -6051,13 +6051,13 @@
       </x:c>
       <x:c r="H153"/>
       <x:c r="I153" t="str">
-        <x:v>private estate drone detection</x:v>
+        <x:v>private ranch drone detection</x:v>
       </x:c>
       <x:c r="J153" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K153" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L153"/>
       <x:c r="M153"/>
@@ -6089,13 +6089,13 @@
       </x:c>
       <x:c r="H154"/>
       <x:c r="I154" t="str">
-        <x:v>enterprise anti drone</x:v>
+        <x:v>mine anti drone</x:v>
       </x:c>
       <x:c r="J154" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K154" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L154"/>
       <x:c r="M154"/>
@@ -6127,13 +6127,13 @@
       </x:c>
       <x:c r="H155"/>
       <x:c r="I155" t="str">
-        <x:v>enterprise drone detection</x:v>
+        <x:v>mining site drone detection</x:v>
       </x:c>
       <x:c r="J155" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K155" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L155"/>
       <x:c r="M155"/>
@@ -6165,13 +6165,13 @@
       </x:c>
       <x:c r="H156"/>
       <x:c r="I156" t="str">
-        <x:v>enterprise c-uas</x:v>
+        <x:v>oil refinery anti drone</x:v>
       </x:c>
       <x:c r="J156" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K156" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L156"/>
       <x:c r="M156"/>
@@ -6203,13 +6203,13 @@
       </x:c>
       <x:c r="H157"/>
       <x:c r="I157" t="str">
-        <x:v>enterprise drone detector</x:v>
+        <x:v>oil field drone detector</x:v>
       </x:c>
       <x:c r="J157" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K157" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L157"/>
       <x:c r="M157"/>
@@ -6241,13 +6241,13 @@
       </x:c>
       <x:c r="H158"/>
       <x:c r="I158" t="str">
-        <x:v>corporate headquarters anti drone</x:v>
+        <x:v>factory drone detection</x:v>
       </x:c>
       <x:c r="J158" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K158" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L158"/>
       <x:c r="M158"/>
@@ -6279,13 +6279,13 @@
       </x:c>
       <x:c r="H159"/>
       <x:c r="I159" t="str">
-        <x:v>corporate campus drone detection</x:v>
+        <x:v>industrial park c-uas</x:v>
       </x:c>
       <x:c r="J159" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K159" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L159"/>
       <x:c r="M159"/>
@@ -6317,13 +6317,13 @@
       </x:c>
       <x:c r="H160"/>
       <x:c r="I160" t="str">
-        <x:v>business campus drone security</x:v>
+        <x:v>corporate headquarters anti drone</x:v>
       </x:c>
       <x:c r="J160" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K160" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L160"/>
       <x:c r="M160"/>
@@ -6355,13 +6355,13 @@
       </x:c>
       <x:c r="H161"/>
       <x:c r="I161" t="str">
-        <x:v>enterprise airspace monitoring</x:v>
+        <x:v>warehouse drone security</x:v>
       </x:c>
       <x:c r="J161" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K161" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L161"/>
       <x:c r="M161"/>
@@ -6393,13 +6393,13 @@
       </x:c>
       <x:c r="H162"/>
       <x:c r="I162" t="str">
-        <x:v>critical infrastructure anti drone</x:v>
+        <x:v>government building anti drone</x:v>
       </x:c>
       <x:c r="J162" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K162" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L162"/>
       <x:c r="M162"/>
@@ -6431,13 +6431,13 @@
       </x:c>
       <x:c r="H163"/>
       <x:c r="I163" t="str">
-        <x:v>critical infrastructure drone detection</x:v>
+        <x:v>data center drone detection</x:v>
       </x:c>
       <x:c r="J163" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K163" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L163"/>
       <x:c r="M163"/>
@@ -6469,13 +6469,13 @@
       </x:c>
       <x:c r="H164"/>
       <x:c r="I164" t="str">
-        <x:v>critical infrastructure c-uas</x:v>
+        <x:v>telecom tower drone detector</x:v>
       </x:c>
       <x:c r="J164" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K164" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L164"/>
       <x:c r="M164"/>
@@ -6507,13 +6507,13 @@
       </x:c>
       <x:c r="H165"/>
       <x:c r="I165" t="str">
-        <x:v>critical infrastructure drone detector</x:v>
+        <x:v>water treatment plant anti drone</x:v>
       </x:c>
       <x:c r="J165" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K165" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L165"/>
       <x:c r="M165"/>
@@ -6545,13 +6545,13 @@
       </x:c>
       <x:c r="H166"/>
       <x:c r="I166" t="str">
-        <x:v>critical infrastructure airspace monitoring</x:v>
+        <x:v>dam drone detection</x:v>
       </x:c>
       <x:c r="J166" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K166" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L166"/>
       <x:c r="M166"/>
@@ -6583,13 +6583,13 @@
       </x:c>
       <x:c r="H167"/>
       <x:c r="I167" t="str">
-        <x:v>critical infrastructure counter drone</x:v>
+        <x:v>railway station anti drone</x:v>
       </x:c>
       <x:c r="J167" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K167" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L167"/>
       <x:c r="M167"/>
@@ -6621,13 +6621,13 @@
       </x:c>
       <x:c r="H168"/>
       <x:c r="I168" t="str">
-        <x:v>critical facility drone security</x:v>
+        <x:v>metro station drone detector</x:v>
       </x:c>
       <x:c r="J168" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K168" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L168"/>
       <x:c r="M168"/>
@@ -6659,13 +6659,13 @@
       </x:c>
       <x:c r="H169"/>
       <x:c r="I169" t="str">
-        <x:v>critical asset drone monitoring</x:v>
+        <x:v>bridge c-uas</x:v>
       </x:c>
       <x:c r="J169" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K169" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L169"/>
       <x:c r="M169"/>
@@ -6697,13 +6697,13 @@
       </x:c>
       <x:c r="H170"/>
       <x:c r="I170" t="str">
-        <x:v>power plant anti drone</x:v>
+        <x:v>nuclear power plant anti drone</x:v>
       </x:c>
       <x:c r="J170" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K170" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L170"/>
       <x:c r="M170"/>
@@ -6735,13 +6735,13 @@
       </x:c>
       <x:c r="H171"/>
       <x:c r="I171" t="str">
-        <x:v>power plant drone detection</x:v>
+        <x:v>thermal power plant drone detection</x:v>
       </x:c>
       <x:c r="J171" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K171" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L171"/>
       <x:c r="M171"/>
@@ -6773,13 +6773,13 @@
       </x:c>
       <x:c r="H172"/>
       <x:c r="I172" t="str">
-        <x:v>power plant c-uas</x:v>
+        <x:v>hydroelectric power plant drone detector</x:v>
       </x:c>
       <x:c r="J172" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K172" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L172"/>
       <x:c r="M172"/>
@@ -6811,13 +6811,13 @@
       </x:c>
       <x:c r="H173"/>
       <x:c r="I173" t="str">
-        <x:v>power plant drone detector</x:v>
+        <x:v>solar farm anti drone</x:v>
       </x:c>
       <x:c r="J173" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K173" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L173"/>
       <x:c r="M173"/>
@@ -6849,13 +6849,13 @@
       </x:c>
       <x:c r="H174"/>
       <x:c r="I174" t="str">
-        <x:v>power plant airspace monitoring</x:v>
+        <x:v>wind farm drone detection</x:v>
       </x:c>
       <x:c r="J174" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K174" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L174"/>
       <x:c r="M174"/>
@@ -6887,13 +6887,13 @@
       </x:c>
       <x:c r="H175"/>
       <x:c r="I175" t="str">
-        <x:v>energy facility anti drone</x:v>
+        <x:v>power substation drone detector</x:v>
       </x:c>
       <x:c r="J175" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K175" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L175"/>
       <x:c r="M175"/>
@@ -6925,13 +6925,13 @@
       </x:c>
       <x:c r="H176"/>
       <x:c r="I176" t="str">
-        <x:v>power grid drone detection</x:v>
+        <x:v>electric grid c-uas</x:v>
       </x:c>
       <x:c r="J176" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K176" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L176"/>
       <x:c r="M176"/>
@@ -6963,13 +6963,13 @@
       </x:c>
       <x:c r="H177"/>
       <x:c r="I177" t="str">
-        <x:v>substation drone monitoring</x:v>
+        <x:v>power station anti drone</x:v>
       </x:c>
       <x:c r="J177" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K177" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L177"/>
       <x:c r="M177"/>
@@ -7007,7 +7007,7 @@
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K178" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L178"/>
       <x:c r="M178"/>
@@ -7045,7 +7045,7 @@
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K179" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L179"/>
       <x:c r="M179"/>
@@ -7077,13 +7077,13 @@
       </x:c>
       <x:c r="H180"/>
       <x:c r="I180" t="str">
-        <x:v>airport drone detection</x:v>
+        <x:v>runway drone detection</x:v>
       </x:c>
       <x:c r="J180" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K180" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L180"/>
       <x:c r="M180"/>
@@ -7115,13 +7115,13 @@
       </x:c>
       <x:c r="H181"/>
       <x:c r="I181" t="str">
-        <x:v>airport c-uas</x:v>
+        <x:v>airfield drone detector</x:v>
       </x:c>
       <x:c r="J181" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K181" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L181"/>
       <x:c r="M181"/>
@@ -7153,13 +7153,13 @@
       </x:c>
       <x:c r="H182"/>
       <x:c r="I182" t="str">
-        <x:v>airport drone detector</x:v>
+        <x:v>airport perimeter anti drone</x:v>
       </x:c>
       <x:c r="J182" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K182" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L182"/>
       <x:c r="M182"/>
@@ -7191,13 +7191,13 @@
       </x:c>
       <x:c r="H183"/>
       <x:c r="I183" t="str">
-        <x:v>airport airspace monitoring</x:v>
+        <x:v>airport c-uas</x:v>
       </x:c>
       <x:c r="J183" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K183" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L183"/>
       <x:c r="M183"/>
@@ -7229,13 +7229,13 @@
       </x:c>
       <x:c r="H184"/>
       <x:c r="I184" t="str">
-        <x:v>runway drone detection</x:v>
+        <x:v>heliport drone detection</x:v>
       </x:c>
       <x:c r="J184" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K184" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L184"/>
       <x:c r="M184"/>
@@ -7267,13 +7267,13 @@
       </x:c>
       <x:c r="H185"/>
       <x:c r="I185" t="str">
-        <x:v>airport counter drone</x:v>
+        <x:v>aviation facility drone security</x:v>
       </x:c>
       <x:c r="J185" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K185" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L185"/>
       <x:c r="M185"/>
@@ -7305,13 +7305,13 @@
       </x:c>
       <x:c r="H186"/>
       <x:c r="I186" t="str">
-        <x:v>border anti drone</x:v>
+        <x:v>border checkpoint anti drone</x:v>
       </x:c>
       <x:c r="J186" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K186" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L186"/>
       <x:c r="M186"/>
@@ -7343,13 +7343,13 @@
       </x:c>
       <x:c r="H187"/>
       <x:c r="I187" t="str">
-        <x:v>border drone detection</x:v>
+        <x:v>border post drone detection</x:v>
       </x:c>
       <x:c r="J187" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K187" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L187"/>
       <x:c r="M187"/>
@@ -7381,13 +7381,13 @@
       </x:c>
       <x:c r="H188"/>
       <x:c r="I188" t="str">
-        <x:v>border c-uas</x:v>
+        <x:v>border patrol c-uas</x:v>
       </x:c>
       <x:c r="J188" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K188" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L188"/>
       <x:c r="M188"/>
@@ -7419,13 +7419,13 @@
       </x:c>
       <x:c r="H189"/>
       <x:c r="I189" t="str">
-        <x:v>border drone detector</x:v>
+        <x:v>customs checkpoint drone detector</x:v>
       </x:c>
       <x:c r="J189" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K189" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L189"/>
       <x:c r="M189"/>
@@ -7457,13 +7457,13 @@
       </x:c>
       <x:c r="H190"/>
       <x:c r="I190" t="str">
-        <x:v>border airspace monitoring</x:v>
+        <x:v>land border anti drone</x:v>
       </x:c>
       <x:c r="J190" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K190" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L190"/>
       <x:c r="M190"/>
@@ -7495,13 +7495,13 @@
       </x:c>
       <x:c r="H191"/>
       <x:c r="I191" t="str">
-        <x:v>border counter drone</x:v>
+        <x:v>coastal border drone detection</x:v>
       </x:c>
       <x:c r="J191" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K191" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L191"/>
       <x:c r="M191"/>
@@ -7533,13 +7533,13 @@
       </x:c>
       <x:c r="H192"/>
       <x:c r="I192" t="str">
-        <x:v>border patrol drone detection</x:v>
+        <x:v>remote border post drone security</x:v>
       </x:c>
       <x:c r="J192" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K192" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L192"/>
       <x:c r="M192"/>
@@ -7571,13 +7571,13 @@
       </x:c>
       <x:c r="H193"/>
       <x:c r="I193" t="str">
-        <x:v>frontier drone monitoring</x:v>
+        <x:v>frontier drone detector</x:v>
       </x:c>
       <x:c r="J193" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K193" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L193"/>
       <x:c r="M193"/>
@@ -7609,13 +7609,13 @@
       </x:c>
       <x:c r="H194"/>
       <x:c r="I194" t="str">
-        <x:v>public safety anti drone</x:v>
+        <x:v>police station anti drone</x:v>
       </x:c>
       <x:c r="J194" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K194" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L194"/>
       <x:c r="M194"/>
@@ -7647,13 +7647,13 @@
       </x:c>
       <x:c r="H195"/>
       <x:c r="I195" t="str">
-        <x:v>public safety drone detection</x:v>
+        <x:v>law enforcement drone detection</x:v>
       </x:c>
       <x:c r="J195" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K195" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L195"/>
       <x:c r="M195"/>
@@ -7685,13 +7685,13 @@
       </x:c>
       <x:c r="H196"/>
       <x:c r="I196" t="str">
-        <x:v>public safety c-uas</x:v>
+        <x:v>emergency command center anti drone</x:v>
       </x:c>
       <x:c r="J196" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K196" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L196"/>
       <x:c r="M196"/>
@@ -7723,13 +7723,13 @@
       </x:c>
       <x:c r="H197"/>
       <x:c r="I197" t="str">
-        <x:v>public safety drone detector</x:v>
+        <x:v>city center drone detector</x:v>
       </x:c>
       <x:c r="J197" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K197" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L197"/>
       <x:c r="M197"/>
@@ -7761,13 +7761,13 @@
       </x:c>
       <x:c r="H198"/>
       <x:c r="I198" t="str">
-        <x:v>law enforcement anti drone</x:v>
+        <x:v>urban security c-uas</x:v>
       </x:c>
       <x:c r="J198" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K198" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L198"/>
       <x:c r="M198"/>
@@ -7799,13 +7799,13 @@
       </x:c>
       <x:c r="H199"/>
       <x:c r="I199" t="str">
-        <x:v>police drone detection</x:v>
+        <x:v>public square drone detection</x:v>
       </x:c>
       <x:c r="J199" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K199" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L199"/>
       <x:c r="M199"/>
@@ -7837,13 +7837,13 @@
       </x:c>
       <x:c r="H200"/>
       <x:c r="I200" t="str">
-        <x:v>emergency response drone monitoring</x:v>
+        <x:v>fire department anti drone</x:v>
       </x:c>
       <x:c r="J200" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K200" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L200"/>
       <x:c r="M200"/>
@@ -7875,13 +7875,13 @@
       </x:c>
       <x:c r="H201"/>
       <x:c r="I201" t="str">
-        <x:v>urban drone security</x:v>
+        <x:v>emergency response drone security</x:v>
       </x:c>
       <x:c r="J201" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K201" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L201"/>
       <x:c r="M201"/>
@@ -7919,7 +7919,7 @@
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K202" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L202"/>
       <x:c r="M202"/>
@@ -7951,13 +7951,13 @@
       </x:c>
       <x:c r="H203"/>
       <x:c r="I203" t="str">
-        <x:v>prison drone detection</x:v>
+        <x:v>correctional facility drone detection</x:v>
       </x:c>
       <x:c r="J203" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K203" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L203"/>
       <x:c r="M203"/>
@@ -7989,13 +7989,13 @@
       </x:c>
       <x:c r="H204"/>
       <x:c r="I204" t="str">
-        <x:v>prison c-uas</x:v>
+        <x:v>jail drone detector</x:v>
       </x:c>
       <x:c r="J204" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K204" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L204"/>
       <x:c r="M204"/>
@@ -8027,13 +8027,13 @@
       </x:c>
       <x:c r="H205"/>
       <x:c r="I205" t="str">
-        <x:v>prison drone detector</x:v>
+        <x:v>detention center anti drone</x:v>
       </x:c>
       <x:c r="J205" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K205" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L205"/>
       <x:c r="M205"/>
@@ -8065,13 +8065,13 @@
       </x:c>
       <x:c r="H206"/>
       <x:c r="I206" t="str">
-        <x:v>prison drone monitoring</x:v>
+        <x:v>prison perimeter c-uas</x:v>
       </x:c>
       <x:c r="J206" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K206" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L206"/>
       <x:c r="M206"/>
@@ -8103,13 +8103,13 @@
       </x:c>
       <x:c r="H207"/>
       <x:c r="I207" t="str">
-        <x:v>correctional facility anti drone</x:v>
+        <x:v>prison contraband drone detection</x:v>
       </x:c>
       <x:c r="J207" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K207" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L207"/>
       <x:c r="M207"/>
@@ -8141,13 +8141,13 @@
       </x:c>
       <x:c r="H208"/>
       <x:c r="I208" t="str">
-        <x:v>contraband drone detection</x:v>
+        <x:v>penitentiary drone security</x:v>
       </x:c>
       <x:c r="J208" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K208" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L208"/>
       <x:c r="M208"/>
@@ -8179,13 +8179,13 @@
       </x:c>
       <x:c r="H209"/>
       <x:c r="I209" t="str">
-        <x:v>prison perimeter drone security</x:v>
+        <x:v>prison drone locator</x:v>
       </x:c>
       <x:c r="J209" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K209" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L209"/>
       <x:c r="M209"/>
@@ -8217,13 +8217,13 @@
       </x:c>
       <x:c r="H210"/>
       <x:c r="I210" t="str">
-        <x:v>port anti drone</x:v>
+        <x:v>seaport anti drone</x:v>
       </x:c>
       <x:c r="J210" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K210" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L210"/>
       <x:c r="M210"/>
@@ -8255,13 +8255,13 @@
       </x:c>
       <x:c r="H211"/>
       <x:c r="I211" t="str">
-        <x:v>port drone detection</x:v>
+        <x:v>harbor drone detection</x:v>
       </x:c>
       <x:c r="J211" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K211" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L211"/>
       <x:c r="M211"/>
@@ -8293,13 +8293,13 @@
       </x:c>
       <x:c r="H212"/>
       <x:c r="I212" t="str">
-        <x:v>port c-uas</x:v>
+        <x:v>container terminal drone detector</x:v>
       </x:c>
       <x:c r="J212" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K212" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L212"/>
       <x:c r="M212"/>
@@ -8331,13 +8331,13 @@
       </x:c>
       <x:c r="H213"/>
       <x:c r="I213" t="str">
-        <x:v>port drone detector</x:v>
+        <x:v>cargo terminal anti drone</x:v>
       </x:c>
       <x:c r="J213" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K213" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L213"/>
       <x:c r="M213"/>
@@ -8369,13 +8369,13 @@
       </x:c>
       <x:c r="H214"/>
       <x:c r="I214" t="str">
-        <x:v>port airspace monitoring</x:v>
+        <x:v>oil port drone detection</x:v>
       </x:c>
       <x:c r="J214" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K214" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L214"/>
       <x:c r="M214"/>
@@ -8407,13 +8407,13 @@
       </x:c>
       <x:c r="H215"/>
       <x:c r="I215" t="str">
-        <x:v>seaport anti drone</x:v>
+        <x:v>port warehouse drone security</x:v>
       </x:c>
       <x:c r="J215" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K215" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L215"/>
       <x:c r="M215"/>
@@ -8445,13 +8445,13 @@
       </x:c>
       <x:c r="H216"/>
       <x:c r="I216" t="str">
-        <x:v>harbor drone detection</x:v>
+        <x:v>port c-uas</x:v>
       </x:c>
       <x:c r="J216" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K216" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L216"/>
       <x:c r="M216"/>
@@ -8483,13 +8483,13 @@
       </x:c>
       <x:c r="H217"/>
       <x:c r="I217" t="str">
-        <x:v>port security drone monitoring</x:v>
+        <x:v>shipping terminal drone detection</x:v>
       </x:c>
       <x:c r="J217" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K217" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L217"/>
       <x:c r="M217"/>
@@ -8521,13 +8521,13 @@
       </x:c>
       <x:c r="H218"/>
       <x:c r="I218" t="str">
-        <x:v>mass event anti drone</x:v>
+        <x:v>stadium anti drone</x:v>
       </x:c>
       <x:c r="J218" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K218" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L218"/>
       <x:c r="M218"/>
@@ -8559,13 +8559,13 @@
       </x:c>
       <x:c r="H219"/>
       <x:c r="I219" t="str">
-        <x:v>mass event drone detection</x:v>
+        <x:v>football stadium drone detection</x:v>
       </x:c>
       <x:c r="J219" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K219" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L219"/>
       <x:c r="M219"/>
@@ -8597,13 +8597,13 @@
       </x:c>
       <x:c r="H220"/>
       <x:c r="I220" t="str">
-        <x:v>mass event c-uas</x:v>
+        <x:v>sports event c-uas</x:v>
       </x:c>
       <x:c r="J220" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K220" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L220"/>
       <x:c r="M220"/>
@@ -8635,13 +8635,13 @@
       </x:c>
       <x:c r="H221"/>
       <x:c r="I221" t="str">
-        <x:v>stadium anti drone</x:v>
+        <x:v>concert drone detector</x:v>
       </x:c>
       <x:c r="J221" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K221" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L221"/>
       <x:c r="M221"/>
@@ -8673,13 +8673,13 @@
       </x:c>
       <x:c r="H222"/>
       <x:c r="I222" t="str">
-        <x:v>stadium drone detection</x:v>
+        <x:v>music festival anti drone</x:v>
       </x:c>
       <x:c r="J222" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K222" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L222"/>
       <x:c r="M222"/>
@@ -8711,13 +8711,13 @@
       </x:c>
       <x:c r="H223"/>
       <x:c r="I223" t="str">
-        <x:v>sports event drone security</x:v>
+        <x:v>convention center drone detection</x:v>
       </x:c>
       <x:c r="J223" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K223" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L223"/>
       <x:c r="M223"/>
@@ -8749,13 +8749,13 @@
       </x:c>
       <x:c r="H224"/>
       <x:c r="I224" t="str">
-        <x:v>concert drone detection</x:v>
+        <x:v>exhibition center anti drone</x:v>
       </x:c>
       <x:c r="J224" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K224" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L224"/>
       <x:c r="M224"/>
@@ -8787,13 +8787,13 @@
       </x:c>
       <x:c r="H225"/>
       <x:c r="I225" t="str">
-        <x:v>crowded event drone detection</x:v>
+        <x:v>large event drone security</x:v>
       </x:c>
       <x:c r="J225" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K225" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L225"/>
       <x:c r="M225"/>
@@ -8825,13 +8825,13 @@
       </x:c>
       <x:c r="H226"/>
       <x:c r="I226" t="str">
-        <x:v>vip anti drone</x:v>
+        <x:v>villa anti drone</x:v>
       </x:c>
       <x:c r="J226" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K226" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L226"/>
       <x:c r="M226"/>
@@ -8863,13 +8863,13 @@
       </x:c>
       <x:c r="H227"/>
       <x:c r="I227" t="str">
-        <x:v>vip drone detection</x:v>
+        <x:v>luxury villa drone detection</x:v>
       </x:c>
       <x:c r="J227" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K227" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L227"/>
       <x:c r="M227"/>
@@ -8901,13 +8901,13 @@
       </x:c>
       <x:c r="H228"/>
       <x:c r="I228" t="str">
-        <x:v>vip c-uas</x:v>
+        <x:v>private estate drone detector</x:v>
       </x:c>
       <x:c r="J228" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K228" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L228"/>
       <x:c r="M228"/>
@@ -8939,13 +8939,13 @@
       </x:c>
       <x:c r="H229"/>
       <x:c r="I229" t="str">
-        <x:v>vip drone detector</x:v>
+        <x:v>mansion anti drone</x:v>
       </x:c>
       <x:c r="J229" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K229" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L229"/>
       <x:c r="M229"/>
@@ -8977,13 +8977,13 @@
       </x:c>
       <x:c r="H230"/>
       <x:c r="I230" t="str">
-        <x:v>private property anti drone</x:v>
+        <x:v>private residence c-uas</x:v>
       </x:c>
       <x:c r="J230" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K230" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L230"/>
       <x:c r="M230"/>
@@ -9015,13 +9015,13 @@
       </x:c>
       <x:c r="H231"/>
       <x:c r="I231" t="str">
-        <x:v>private property drone detection</x:v>
+        <x:v>vip convoy drone security</x:v>
       </x:c>
       <x:c r="J231" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K231" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L231"/>
       <x:c r="M231"/>
@@ -9053,13 +9053,13 @@
       </x:c>
       <x:c r="H232"/>
       <x:c r="I232" t="str">
-        <x:v>vip convoy drone security</x:v>
+        <x:v>yacht anti drone</x:v>
       </x:c>
       <x:c r="J232" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K232" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L232"/>
       <x:c r="M232"/>
@@ -9091,13 +9091,13 @@
       </x:c>
       <x:c r="H233"/>
       <x:c r="I233" t="str">
-        <x:v>private estate drone detection</x:v>
+        <x:v>private ranch drone detection</x:v>
       </x:c>
       <x:c r="J233" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K233" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L233"/>
       <x:c r="M233"/>
@@ -9129,13 +9129,13 @@
       </x:c>
       <x:c r="H234"/>
       <x:c r="I234" t="str">
-        <x:v>enterprise anti drone</x:v>
+        <x:v>mine anti drone</x:v>
       </x:c>
       <x:c r="J234" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K234" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L234"/>
       <x:c r="M234"/>
@@ -9167,13 +9167,13 @@
       </x:c>
       <x:c r="H235"/>
       <x:c r="I235" t="str">
-        <x:v>enterprise drone detection</x:v>
+        <x:v>mining site drone detection</x:v>
       </x:c>
       <x:c r="J235" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K235" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L235"/>
       <x:c r="M235"/>
@@ -9205,13 +9205,13 @@
       </x:c>
       <x:c r="H236"/>
       <x:c r="I236" t="str">
-        <x:v>enterprise c-uas</x:v>
+        <x:v>oil refinery anti drone</x:v>
       </x:c>
       <x:c r="J236" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K236" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L236"/>
       <x:c r="M236"/>
@@ -9243,13 +9243,13 @@
       </x:c>
       <x:c r="H237"/>
       <x:c r="I237" t="str">
-        <x:v>enterprise drone detector</x:v>
+        <x:v>oil field drone detector</x:v>
       </x:c>
       <x:c r="J237" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K237" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L237"/>
       <x:c r="M237"/>
@@ -9281,13 +9281,13 @@
       </x:c>
       <x:c r="H238"/>
       <x:c r="I238" t="str">
-        <x:v>corporate headquarters anti drone</x:v>
+        <x:v>factory drone detection</x:v>
       </x:c>
       <x:c r="J238" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K238" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L238"/>
       <x:c r="M238"/>
@@ -9319,13 +9319,13 @@
       </x:c>
       <x:c r="H239"/>
       <x:c r="I239" t="str">
-        <x:v>corporate campus drone detection</x:v>
+        <x:v>industrial park c-uas</x:v>
       </x:c>
       <x:c r="J239" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K239" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L239"/>
       <x:c r="M239"/>
@@ -9357,13 +9357,13 @@
       </x:c>
       <x:c r="H240"/>
       <x:c r="I240" t="str">
-        <x:v>business campus drone security</x:v>
+        <x:v>corporate headquarters anti drone</x:v>
       </x:c>
       <x:c r="J240" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K240" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L240"/>
       <x:c r="M240"/>
@@ -9395,13 +9395,13 @@
       </x:c>
       <x:c r="H241"/>
       <x:c r="I241" t="str">
-        <x:v>enterprise airspace monitoring</x:v>
+        <x:v>warehouse drone security</x:v>
       </x:c>
       <x:c r="J241" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K241" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L241"/>
       <x:c r="M241"/>
@@ -9433,13 +9433,13 @@
       </x:c>
       <x:c r="H242"/>
       <x:c r="I242" t="str">
-        <x:v>critical infrastructure anti drone</x:v>
+        <x:v>government building anti drone</x:v>
       </x:c>
       <x:c r="J242" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K242" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L242"/>
       <x:c r="M242"/>
@@ -9471,13 +9471,13 @@
       </x:c>
       <x:c r="H243"/>
       <x:c r="I243" t="str">
-        <x:v>critical infrastructure drone detection</x:v>
+        <x:v>data center drone detection</x:v>
       </x:c>
       <x:c r="J243" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K243" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L243"/>
       <x:c r="M243"/>
@@ -9509,13 +9509,13 @@
       </x:c>
       <x:c r="H244"/>
       <x:c r="I244" t="str">
-        <x:v>critical infrastructure c-uas</x:v>
+        <x:v>telecom tower drone detector</x:v>
       </x:c>
       <x:c r="J244" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K244" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L244"/>
       <x:c r="M244"/>
@@ -9547,13 +9547,13 @@
       </x:c>
       <x:c r="H245"/>
       <x:c r="I245" t="str">
-        <x:v>critical infrastructure drone detector</x:v>
+        <x:v>water treatment plant anti drone</x:v>
       </x:c>
       <x:c r="J245" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K245" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L245"/>
       <x:c r="M245"/>
@@ -9585,13 +9585,13 @@
       </x:c>
       <x:c r="H246"/>
       <x:c r="I246" t="str">
-        <x:v>critical infrastructure airspace monitoring</x:v>
+        <x:v>dam drone detection</x:v>
       </x:c>
       <x:c r="J246" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K246" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L246"/>
       <x:c r="M246"/>
@@ -9623,13 +9623,13 @@
       </x:c>
       <x:c r="H247"/>
       <x:c r="I247" t="str">
-        <x:v>critical infrastructure counter drone</x:v>
+        <x:v>railway station anti drone</x:v>
       </x:c>
       <x:c r="J247" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K247" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L247"/>
       <x:c r="M247"/>
@@ -9661,13 +9661,13 @@
       </x:c>
       <x:c r="H248"/>
       <x:c r="I248" t="str">
-        <x:v>critical facility drone security</x:v>
+        <x:v>metro station drone detector</x:v>
       </x:c>
       <x:c r="J248" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K248" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L248"/>
       <x:c r="M248"/>
@@ -9699,13 +9699,13 @@
       </x:c>
       <x:c r="H249"/>
       <x:c r="I249" t="str">
-        <x:v>critical asset drone monitoring</x:v>
+        <x:v>bridge c-uas</x:v>
       </x:c>
       <x:c r="J249" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K249" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L249"/>
       <x:c r="M249"/>
@@ -9737,13 +9737,13 @@
       </x:c>
       <x:c r="H250"/>
       <x:c r="I250" t="str">
-        <x:v>power plant anti drone</x:v>
+        <x:v>nuclear power plant anti drone</x:v>
       </x:c>
       <x:c r="J250" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K250" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L250"/>
       <x:c r="M250"/>
@@ -9775,13 +9775,13 @@
       </x:c>
       <x:c r="H251"/>
       <x:c r="I251" t="str">
-        <x:v>power plant drone detection</x:v>
+        <x:v>thermal power plant drone detection</x:v>
       </x:c>
       <x:c r="J251" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K251" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L251"/>
       <x:c r="M251"/>
@@ -9813,13 +9813,13 @@
       </x:c>
       <x:c r="H252"/>
       <x:c r="I252" t="str">
-        <x:v>power plant c-uas</x:v>
+        <x:v>hydroelectric power plant drone detector</x:v>
       </x:c>
       <x:c r="J252" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K252" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L252"/>
       <x:c r="M252"/>
@@ -9851,13 +9851,13 @@
       </x:c>
       <x:c r="H253"/>
       <x:c r="I253" t="str">
-        <x:v>power plant drone detector</x:v>
+        <x:v>solar farm anti drone</x:v>
       </x:c>
       <x:c r="J253" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K253" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L253"/>
       <x:c r="M253"/>
@@ -9889,13 +9889,13 @@
       </x:c>
       <x:c r="H254"/>
       <x:c r="I254" t="str">
-        <x:v>power plant airspace monitoring</x:v>
+        <x:v>wind farm drone detection</x:v>
       </x:c>
       <x:c r="J254" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K254" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L254"/>
       <x:c r="M254"/>
@@ -9927,13 +9927,13 @@
       </x:c>
       <x:c r="H255"/>
       <x:c r="I255" t="str">
-        <x:v>energy facility anti drone</x:v>
+        <x:v>power substation drone detector</x:v>
       </x:c>
       <x:c r="J255" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K255" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L255"/>
       <x:c r="M255"/>
@@ -9965,13 +9965,13 @@
       </x:c>
       <x:c r="H256"/>
       <x:c r="I256" t="str">
-        <x:v>power grid drone detection</x:v>
+        <x:v>electric grid c-uas</x:v>
       </x:c>
       <x:c r="J256" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K256" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L256"/>
       <x:c r="M256"/>
@@ -10003,13 +10003,13 @@
       </x:c>
       <x:c r="H257"/>
       <x:c r="I257" t="str">
-        <x:v>substation drone monitoring</x:v>
+        <x:v>power station anti drone</x:v>
       </x:c>
       <x:c r="J257" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K257" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L257"/>
       <x:c r="M257"/>
@@ -10047,7 +10047,7 @@
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K258" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L258"/>
       <x:c r="M258"/>
@@ -10085,7 +10085,7 @@
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K259" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L259"/>
       <x:c r="M259"/>
@@ -10117,13 +10117,13 @@
       </x:c>
       <x:c r="H260"/>
       <x:c r="I260" t="str">
-        <x:v>airport drone detection</x:v>
+        <x:v>runway drone detection</x:v>
       </x:c>
       <x:c r="J260" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K260" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L260"/>
       <x:c r="M260"/>
@@ -10155,13 +10155,13 @@
       </x:c>
       <x:c r="H261"/>
       <x:c r="I261" t="str">
-        <x:v>airport c-uas</x:v>
+        <x:v>airfield drone detector</x:v>
       </x:c>
       <x:c r="J261" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K261" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L261"/>
       <x:c r="M261"/>
@@ -10193,13 +10193,13 @@
       </x:c>
       <x:c r="H262"/>
       <x:c r="I262" t="str">
-        <x:v>airport drone detector</x:v>
+        <x:v>airport perimeter anti drone</x:v>
       </x:c>
       <x:c r="J262" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K262" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L262"/>
       <x:c r="M262"/>
@@ -10231,13 +10231,13 @@
       </x:c>
       <x:c r="H263"/>
       <x:c r="I263" t="str">
-        <x:v>airport airspace monitoring</x:v>
+        <x:v>airport c-uas</x:v>
       </x:c>
       <x:c r="J263" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K263" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L263"/>
       <x:c r="M263"/>
@@ -10269,13 +10269,13 @@
       </x:c>
       <x:c r="H264"/>
       <x:c r="I264" t="str">
-        <x:v>runway drone detection</x:v>
+        <x:v>heliport drone detection</x:v>
       </x:c>
       <x:c r="J264" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K264" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L264"/>
       <x:c r="M264"/>
@@ -10307,13 +10307,13 @@
       </x:c>
       <x:c r="H265"/>
       <x:c r="I265" t="str">
-        <x:v>airport counter drone</x:v>
+        <x:v>aviation facility drone security</x:v>
       </x:c>
       <x:c r="J265" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K265" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L265"/>
       <x:c r="M265"/>
@@ -10345,13 +10345,13 @@
       </x:c>
       <x:c r="H266"/>
       <x:c r="I266" t="str">
-        <x:v>border anti drone</x:v>
+        <x:v>border checkpoint anti drone</x:v>
       </x:c>
       <x:c r="J266" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K266" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L266"/>
       <x:c r="M266"/>
@@ -10383,13 +10383,13 @@
       </x:c>
       <x:c r="H267"/>
       <x:c r="I267" t="str">
-        <x:v>border drone detection</x:v>
+        <x:v>border post drone detection</x:v>
       </x:c>
       <x:c r="J267" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K267" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L267"/>
       <x:c r="M267"/>
@@ -10421,13 +10421,13 @@
       </x:c>
       <x:c r="H268"/>
       <x:c r="I268" t="str">
-        <x:v>border c-uas</x:v>
+        <x:v>border patrol c-uas</x:v>
       </x:c>
       <x:c r="J268" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K268" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L268"/>
       <x:c r="M268"/>
@@ -10459,13 +10459,13 @@
       </x:c>
       <x:c r="H269"/>
       <x:c r="I269" t="str">
-        <x:v>border drone detector</x:v>
+        <x:v>customs checkpoint drone detector</x:v>
       </x:c>
       <x:c r="J269" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K269" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L269"/>
       <x:c r="M269"/>
@@ -10497,13 +10497,13 @@
       </x:c>
       <x:c r="H270"/>
       <x:c r="I270" t="str">
-        <x:v>border airspace monitoring</x:v>
+        <x:v>land border anti drone</x:v>
       </x:c>
       <x:c r="J270" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K270" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L270"/>
       <x:c r="M270"/>
@@ -10535,13 +10535,13 @@
       </x:c>
       <x:c r="H271"/>
       <x:c r="I271" t="str">
-        <x:v>border counter drone</x:v>
+        <x:v>coastal border drone detection</x:v>
       </x:c>
       <x:c r="J271" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K271" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L271"/>
       <x:c r="M271"/>
@@ -10573,13 +10573,13 @@
       </x:c>
       <x:c r="H272"/>
       <x:c r="I272" t="str">
-        <x:v>border patrol drone detection</x:v>
+        <x:v>remote border post drone security</x:v>
       </x:c>
       <x:c r="J272" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K272" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L272"/>
       <x:c r="M272"/>
@@ -10611,13 +10611,13 @@
       </x:c>
       <x:c r="H273"/>
       <x:c r="I273" t="str">
-        <x:v>frontier drone monitoring</x:v>
+        <x:v>frontier drone detector</x:v>
       </x:c>
       <x:c r="J273" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K273" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L273"/>
       <x:c r="M273"/>
@@ -10649,13 +10649,13 @@
       </x:c>
       <x:c r="H274"/>
       <x:c r="I274" t="str">
-        <x:v>public safety anti drone</x:v>
+        <x:v>police station anti drone</x:v>
       </x:c>
       <x:c r="J274" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K274" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L274"/>
       <x:c r="M274"/>
@@ -10687,13 +10687,13 @@
       </x:c>
       <x:c r="H275"/>
       <x:c r="I275" t="str">
-        <x:v>public safety drone detection</x:v>
+        <x:v>law enforcement drone detection</x:v>
       </x:c>
       <x:c r="J275" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K275" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L275"/>
       <x:c r="M275"/>
@@ -10725,13 +10725,13 @@
       </x:c>
       <x:c r="H276"/>
       <x:c r="I276" t="str">
-        <x:v>public safety c-uas</x:v>
+        <x:v>emergency command center anti drone</x:v>
       </x:c>
       <x:c r="J276" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K276" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L276"/>
       <x:c r="M276"/>
@@ -10763,13 +10763,13 @@
       </x:c>
       <x:c r="H277"/>
       <x:c r="I277" t="str">
-        <x:v>public safety drone detector</x:v>
+        <x:v>city center drone detector</x:v>
       </x:c>
       <x:c r="J277" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K277" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L277"/>
       <x:c r="M277"/>
@@ -10801,13 +10801,13 @@
       </x:c>
       <x:c r="H278"/>
       <x:c r="I278" t="str">
-        <x:v>law enforcement anti drone</x:v>
+        <x:v>urban security c-uas</x:v>
       </x:c>
       <x:c r="J278" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K278" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L278"/>
       <x:c r="M278"/>
@@ -10839,13 +10839,13 @@
       </x:c>
       <x:c r="H279"/>
       <x:c r="I279" t="str">
-        <x:v>police drone detection</x:v>
+        <x:v>public square drone detection</x:v>
       </x:c>
       <x:c r="J279" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K279" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L279"/>
       <x:c r="M279"/>
@@ -10877,13 +10877,13 @@
       </x:c>
       <x:c r="H280"/>
       <x:c r="I280" t="str">
-        <x:v>emergency response drone monitoring</x:v>
+        <x:v>fire department anti drone</x:v>
       </x:c>
       <x:c r="J280" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K280" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L280"/>
       <x:c r="M280"/>
@@ -10915,13 +10915,13 @@
       </x:c>
       <x:c r="H281"/>
       <x:c r="I281" t="str">
-        <x:v>urban drone security</x:v>
+        <x:v>emergency response drone security</x:v>
       </x:c>
       <x:c r="J281" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K281" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L281"/>
       <x:c r="M281"/>
@@ -10959,7 +10959,7 @@
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K282" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L282"/>
       <x:c r="M282"/>
@@ -10991,13 +10991,13 @@
       </x:c>
       <x:c r="H283"/>
       <x:c r="I283" t="str">
-        <x:v>prison drone detection</x:v>
+        <x:v>correctional facility drone detection</x:v>
       </x:c>
       <x:c r="J283" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K283" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L283"/>
       <x:c r="M283"/>
@@ -11029,13 +11029,13 @@
       </x:c>
       <x:c r="H284"/>
       <x:c r="I284" t="str">
-        <x:v>prison c-uas</x:v>
+        <x:v>jail drone detector</x:v>
       </x:c>
       <x:c r="J284" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K284" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L284"/>
       <x:c r="M284"/>
@@ -11067,13 +11067,13 @@
       </x:c>
       <x:c r="H285"/>
       <x:c r="I285" t="str">
-        <x:v>prison drone detector</x:v>
+        <x:v>detention center anti drone</x:v>
       </x:c>
       <x:c r="J285" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K285" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L285"/>
       <x:c r="M285"/>
@@ -11105,13 +11105,13 @@
       </x:c>
       <x:c r="H286"/>
       <x:c r="I286" t="str">
-        <x:v>prison drone monitoring</x:v>
+        <x:v>prison perimeter c-uas</x:v>
       </x:c>
       <x:c r="J286" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K286" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L286"/>
       <x:c r="M286"/>
@@ -11143,13 +11143,13 @@
       </x:c>
       <x:c r="H287"/>
       <x:c r="I287" t="str">
-        <x:v>correctional facility anti drone</x:v>
+        <x:v>prison contraband drone detection</x:v>
       </x:c>
       <x:c r="J287" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K287" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L287"/>
       <x:c r="M287"/>
@@ -11181,13 +11181,13 @@
       </x:c>
       <x:c r="H288"/>
       <x:c r="I288" t="str">
-        <x:v>contraband drone detection</x:v>
+        <x:v>penitentiary drone security</x:v>
       </x:c>
       <x:c r="J288" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K288" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L288"/>
       <x:c r="M288"/>
@@ -11219,13 +11219,13 @@
       </x:c>
       <x:c r="H289"/>
       <x:c r="I289" t="str">
-        <x:v>prison perimeter drone security</x:v>
+        <x:v>prison drone locator</x:v>
       </x:c>
       <x:c r="J289" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K289" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L289"/>
       <x:c r="M289"/>
@@ -11257,13 +11257,13 @@
       </x:c>
       <x:c r="H290"/>
       <x:c r="I290" t="str">
-        <x:v>port anti drone</x:v>
+        <x:v>seaport anti drone</x:v>
       </x:c>
       <x:c r="J290" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K290" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L290"/>
       <x:c r="M290"/>
@@ -11295,13 +11295,13 @@
       </x:c>
       <x:c r="H291"/>
       <x:c r="I291" t="str">
-        <x:v>port drone detection</x:v>
+        <x:v>harbor drone detection</x:v>
       </x:c>
       <x:c r="J291" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K291" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L291"/>
       <x:c r="M291"/>
@@ -11333,13 +11333,13 @@
       </x:c>
       <x:c r="H292"/>
       <x:c r="I292" t="str">
-        <x:v>port c-uas</x:v>
+        <x:v>container terminal drone detector</x:v>
       </x:c>
       <x:c r="J292" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K292" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L292"/>
       <x:c r="M292"/>
@@ -11371,13 +11371,13 @@
       </x:c>
       <x:c r="H293"/>
       <x:c r="I293" t="str">
-        <x:v>port drone detector</x:v>
+        <x:v>cargo terminal anti drone</x:v>
       </x:c>
       <x:c r="J293" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K293" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L293"/>
       <x:c r="M293"/>
@@ -11409,13 +11409,13 @@
       </x:c>
       <x:c r="H294"/>
       <x:c r="I294" t="str">
-        <x:v>port airspace monitoring</x:v>
+        <x:v>oil port drone detection</x:v>
       </x:c>
       <x:c r="J294" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K294" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L294"/>
       <x:c r="M294"/>
@@ -11447,13 +11447,13 @@
       </x:c>
       <x:c r="H295"/>
       <x:c r="I295" t="str">
-        <x:v>seaport anti drone</x:v>
+        <x:v>port warehouse drone security</x:v>
       </x:c>
       <x:c r="J295" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K295" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L295"/>
       <x:c r="M295"/>
@@ -11485,13 +11485,13 @@
       </x:c>
       <x:c r="H296"/>
       <x:c r="I296" t="str">
-        <x:v>harbor drone detection</x:v>
+        <x:v>port c-uas</x:v>
       </x:c>
       <x:c r="J296" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K296" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L296"/>
       <x:c r="M296"/>
@@ -11523,13 +11523,13 @@
       </x:c>
       <x:c r="H297"/>
       <x:c r="I297" t="str">
-        <x:v>port security drone monitoring</x:v>
+        <x:v>shipping terminal drone detection</x:v>
       </x:c>
       <x:c r="J297" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K297" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L297"/>
       <x:c r="M297"/>
@@ -11561,13 +11561,13 @@
       </x:c>
       <x:c r="H298"/>
       <x:c r="I298" t="str">
-        <x:v>mass event anti drone</x:v>
+        <x:v>stadium anti drone</x:v>
       </x:c>
       <x:c r="J298" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K298" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L298"/>
       <x:c r="M298"/>
@@ -11599,13 +11599,13 @@
       </x:c>
       <x:c r="H299"/>
       <x:c r="I299" t="str">
-        <x:v>mass event drone detection</x:v>
+        <x:v>football stadium drone detection</x:v>
       </x:c>
       <x:c r="J299" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K299" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L299"/>
       <x:c r="M299"/>
@@ -11637,13 +11637,13 @@
       </x:c>
       <x:c r="H300"/>
       <x:c r="I300" t="str">
-        <x:v>mass event c-uas</x:v>
+        <x:v>sports event c-uas</x:v>
       </x:c>
       <x:c r="J300" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K300" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L300"/>
       <x:c r="M300"/>
@@ -11675,13 +11675,13 @@
       </x:c>
       <x:c r="H301"/>
       <x:c r="I301" t="str">
-        <x:v>stadium anti drone</x:v>
+        <x:v>concert drone detector</x:v>
       </x:c>
       <x:c r="J301" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K301" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L301"/>
       <x:c r="M301"/>
@@ -11713,13 +11713,13 @@
       </x:c>
       <x:c r="H302"/>
       <x:c r="I302" t="str">
-        <x:v>stadium drone detection</x:v>
+        <x:v>music festival anti drone</x:v>
       </x:c>
       <x:c r="J302" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K302" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L302"/>
       <x:c r="M302"/>
@@ -11751,13 +11751,13 @@
       </x:c>
       <x:c r="H303"/>
       <x:c r="I303" t="str">
-        <x:v>sports event drone security</x:v>
+        <x:v>convention center drone detection</x:v>
       </x:c>
       <x:c r="J303" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K303" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L303"/>
       <x:c r="M303"/>
@@ -11789,13 +11789,13 @@
       </x:c>
       <x:c r="H304"/>
       <x:c r="I304" t="str">
-        <x:v>concert drone detection</x:v>
+        <x:v>exhibition center anti drone</x:v>
       </x:c>
       <x:c r="J304" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K304" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L304"/>
       <x:c r="M304"/>
@@ -11827,13 +11827,13 @@
       </x:c>
       <x:c r="H305"/>
       <x:c r="I305" t="str">
-        <x:v>crowded event drone detection</x:v>
+        <x:v>large event drone security</x:v>
       </x:c>
       <x:c r="J305" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K305" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L305"/>
       <x:c r="M305"/>
@@ -11865,13 +11865,13 @@
       </x:c>
       <x:c r="H306"/>
       <x:c r="I306" t="str">
-        <x:v>vip anti drone</x:v>
+        <x:v>villa anti drone</x:v>
       </x:c>
       <x:c r="J306" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K306" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L306"/>
       <x:c r="M306"/>
@@ -11903,13 +11903,13 @@
       </x:c>
       <x:c r="H307"/>
       <x:c r="I307" t="str">
-        <x:v>vip drone detection</x:v>
+        <x:v>luxury villa drone detection</x:v>
       </x:c>
       <x:c r="J307" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K307" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L307"/>
       <x:c r="M307"/>
@@ -11941,13 +11941,13 @@
       </x:c>
       <x:c r="H308"/>
       <x:c r="I308" t="str">
-        <x:v>vip c-uas</x:v>
+        <x:v>private estate drone detector</x:v>
       </x:c>
       <x:c r="J308" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K308" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L308"/>
       <x:c r="M308"/>
@@ -11979,13 +11979,13 @@
       </x:c>
       <x:c r="H309"/>
       <x:c r="I309" t="str">
-        <x:v>vip drone detector</x:v>
+        <x:v>mansion anti drone</x:v>
       </x:c>
       <x:c r="J309" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K309" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L309"/>
       <x:c r="M309"/>
@@ -12017,13 +12017,13 @@
       </x:c>
       <x:c r="H310"/>
       <x:c r="I310" t="str">
-        <x:v>private property anti drone</x:v>
+        <x:v>private residence c-uas</x:v>
       </x:c>
       <x:c r="J310" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K310" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L310"/>
       <x:c r="M310"/>
@@ -12055,13 +12055,13 @@
       </x:c>
       <x:c r="H311"/>
       <x:c r="I311" t="str">
-        <x:v>private property drone detection</x:v>
+        <x:v>vip convoy drone security</x:v>
       </x:c>
       <x:c r="J311" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K311" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L311"/>
       <x:c r="M311"/>
@@ -12093,13 +12093,13 @@
       </x:c>
       <x:c r="H312"/>
       <x:c r="I312" t="str">
-        <x:v>vip convoy drone security</x:v>
+        <x:v>yacht anti drone</x:v>
       </x:c>
       <x:c r="J312" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K312" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L312"/>
       <x:c r="M312"/>
@@ -12131,13 +12131,13 @@
       </x:c>
       <x:c r="H313"/>
       <x:c r="I313" t="str">
-        <x:v>private estate drone detection</x:v>
+        <x:v>private ranch drone detection</x:v>
       </x:c>
       <x:c r="J313" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K313" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L313"/>
       <x:c r="M313"/>
@@ -12169,13 +12169,13 @@
       </x:c>
       <x:c r="H314"/>
       <x:c r="I314" t="str">
-        <x:v>enterprise anti drone</x:v>
+        <x:v>mine anti drone</x:v>
       </x:c>
       <x:c r="J314" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K314" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L314"/>
       <x:c r="M314"/>
@@ -12207,13 +12207,13 @@
       </x:c>
       <x:c r="H315"/>
       <x:c r="I315" t="str">
-        <x:v>enterprise drone detection</x:v>
+        <x:v>mining site drone detection</x:v>
       </x:c>
       <x:c r="J315" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K315" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L315"/>
       <x:c r="M315"/>
@@ -12245,13 +12245,13 @@
       </x:c>
       <x:c r="H316"/>
       <x:c r="I316" t="str">
-        <x:v>enterprise c-uas</x:v>
+        <x:v>oil refinery anti drone</x:v>
       </x:c>
       <x:c r="J316" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K316" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L316"/>
       <x:c r="M316"/>
@@ -12283,13 +12283,13 @@
       </x:c>
       <x:c r="H317"/>
       <x:c r="I317" t="str">
-        <x:v>enterprise drone detector</x:v>
+        <x:v>oil field drone detector</x:v>
       </x:c>
       <x:c r="J317" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K317" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L317"/>
       <x:c r="M317"/>
@@ -12321,13 +12321,13 @@
       </x:c>
       <x:c r="H318"/>
       <x:c r="I318" t="str">
-        <x:v>corporate headquarters anti drone</x:v>
+        <x:v>factory drone detection</x:v>
       </x:c>
       <x:c r="J318" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K318" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L318"/>
       <x:c r="M318"/>
@@ -12359,13 +12359,13 @@
       </x:c>
       <x:c r="H319"/>
       <x:c r="I319" t="str">
-        <x:v>corporate campus drone detection</x:v>
+        <x:v>industrial park c-uas</x:v>
       </x:c>
       <x:c r="J319" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K319" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L319"/>
       <x:c r="M319"/>
@@ -12397,13 +12397,13 @@
       </x:c>
       <x:c r="H320"/>
       <x:c r="I320" t="str">
-        <x:v>business campus drone security</x:v>
+        <x:v>corporate headquarters anti drone</x:v>
       </x:c>
       <x:c r="J320" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K320" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L320"/>
       <x:c r="M320"/>
@@ -12435,13 +12435,13 @@
       </x:c>
       <x:c r="H321"/>
       <x:c r="I321" t="str">
-        <x:v>enterprise airspace monitoring</x:v>
+        <x:v>warehouse drone security</x:v>
       </x:c>
       <x:c r="J321" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K321" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L321"/>
       <x:c r="M321"/>
@@ -12473,13 +12473,13 @@
       </x:c>
       <x:c r="H322"/>
       <x:c r="I322" t="str">
-        <x:v>critical infrastructure anti drone</x:v>
+        <x:v>government building anti drone</x:v>
       </x:c>
       <x:c r="J322" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K322" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L322"/>
       <x:c r="M322"/>
@@ -12511,13 +12511,13 @@
       </x:c>
       <x:c r="H323"/>
       <x:c r="I323" t="str">
-        <x:v>critical infrastructure drone detection</x:v>
+        <x:v>data center drone detection</x:v>
       </x:c>
       <x:c r="J323" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K323" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L323"/>
       <x:c r="M323"/>
@@ -12549,13 +12549,13 @@
       </x:c>
       <x:c r="H324"/>
       <x:c r="I324" t="str">
-        <x:v>critical infrastructure c-uas</x:v>
+        <x:v>telecom tower drone detector</x:v>
       </x:c>
       <x:c r="J324" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K324" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L324"/>
       <x:c r="M324"/>
@@ -12587,13 +12587,13 @@
       </x:c>
       <x:c r="H325"/>
       <x:c r="I325" t="str">
-        <x:v>critical infrastructure drone detector</x:v>
+        <x:v>water treatment plant anti drone</x:v>
       </x:c>
       <x:c r="J325" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K325" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L325"/>
       <x:c r="M325"/>
@@ -12625,13 +12625,13 @@
       </x:c>
       <x:c r="H326"/>
       <x:c r="I326" t="str">
-        <x:v>critical infrastructure airspace monitoring</x:v>
+        <x:v>dam drone detection</x:v>
       </x:c>
       <x:c r="J326" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K326" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L326"/>
       <x:c r="M326"/>
@@ -12663,13 +12663,13 @@
       </x:c>
       <x:c r="H327"/>
       <x:c r="I327" t="str">
-        <x:v>critical infrastructure counter drone</x:v>
+        <x:v>railway station anti drone</x:v>
       </x:c>
       <x:c r="J327" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K327" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L327"/>
       <x:c r="M327"/>
@@ -12701,13 +12701,13 @@
       </x:c>
       <x:c r="H328"/>
       <x:c r="I328" t="str">
-        <x:v>critical facility drone security</x:v>
+        <x:v>metro station drone detector</x:v>
       </x:c>
       <x:c r="J328" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K328" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L328"/>
       <x:c r="M328"/>
@@ -12739,13 +12739,13 @@
       </x:c>
       <x:c r="H329"/>
       <x:c r="I329" t="str">
-        <x:v>critical asset drone monitoring</x:v>
+        <x:v>bridge c-uas</x:v>
       </x:c>
       <x:c r="J329" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K329" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L329"/>
       <x:c r="M329"/>
@@ -12777,13 +12777,13 @@
       </x:c>
       <x:c r="H330"/>
       <x:c r="I330" t="str">
-        <x:v>power plant anti drone</x:v>
+        <x:v>nuclear power plant anti drone</x:v>
       </x:c>
       <x:c r="J330" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K330" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L330"/>
       <x:c r="M330"/>
@@ -12815,13 +12815,13 @@
       </x:c>
       <x:c r="H331"/>
       <x:c r="I331" t="str">
-        <x:v>power plant drone detection</x:v>
+        <x:v>thermal power plant drone detection</x:v>
       </x:c>
       <x:c r="J331" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K331" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L331"/>
       <x:c r="M331"/>
@@ -12853,13 +12853,13 @@
       </x:c>
       <x:c r="H332"/>
       <x:c r="I332" t="str">
-        <x:v>power plant c-uas</x:v>
+        <x:v>hydroelectric power plant drone detector</x:v>
       </x:c>
       <x:c r="J332" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K332" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L332"/>
       <x:c r="M332"/>
@@ -12891,13 +12891,13 @@
       </x:c>
       <x:c r="H333"/>
       <x:c r="I333" t="str">
-        <x:v>power plant drone detector</x:v>
+        <x:v>solar farm anti drone</x:v>
       </x:c>
       <x:c r="J333" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K333" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L333"/>
       <x:c r="M333"/>
@@ -12929,13 +12929,13 @@
       </x:c>
       <x:c r="H334"/>
       <x:c r="I334" t="str">
-        <x:v>power plant airspace monitoring</x:v>
+        <x:v>wind farm drone detection</x:v>
       </x:c>
       <x:c r="J334" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K334" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L334"/>
       <x:c r="M334"/>
@@ -12967,13 +12967,13 @@
       </x:c>
       <x:c r="H335"/>
       <x:c r="I335" t="str">
-        <x:v>energy facility anti drone</x:v>
+        <x:v>power substation drone detector</x:v>
       </x:c>
       <x:c r="J335" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K335" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L335"/>
       <x:c r="M335"/>
@@ -13005,13 +13005,13 @@
       </x:c>
       <x:c r="H336"/>
       <x:c r="I336" t="str">
-        <x:v>power grid drone detection</x:v>
+        <x:v>electric grid c-uas</x:v>
       </x:c>
       <x:c r="J336" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K336" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L336"/>
       <x:c r="M336"/>
@@ -13043,13 +13043,13 @@
       </x:c>
       <x:c r="H337"/>
       <x:c r="I337" t="str">
-        <x:v>substation drone monitoring</x:v>
+        <x:v>power station anti drone</x:v>
       </x:c>
       <x:c r="J337" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K337" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L337"/>
       <x:c r="M337"/>
@@ -13087,7 +13087,7 @@
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K338" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L338"/>
       <x:c r="M338"/>
@@ -13125,7 +13125,7 @@
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K339" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L339"/>
       <x:c r="M339"/>
@@ -13157,13 +13157,13 @@
       </x:c>
       <x:c r="H340"/>
       <x:c r="I340" t="str">
-        <x:v>airport drone detection</x:v>
+        <x:v>runway drone detection</x:v>
       </x:c>
       <x:c r="J340" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K340" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L340"/>
       <x:c r="M340"/>
@@ -13195,13 +13195,13 @@
       </x:c>
       <x:c r="H341"/>
       <x:c r="I341" t="str">
-        <x:v>airport c-uas</x:v>
+        <x:v>airfield drone detector</x:v>
       </x:c>
       <x:c r="J341" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K341" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L341"/>
       <x:c r="M341"/>
@@ -13233,13 +13233,13 @@
       </x:c>
       <x:c r="H342"/>
       <x:c r="I342" t="str">
-        <x:v>airport drone detector</x:v>
+        <x:v>airport perimeter anti drone</x:v>
       </x:c>
       <x:c r="J342" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K342" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L342"/>
       <x:c r="M342"/>
@@ -13271,13 +13271,13 @@
       </x:c>
       <x:c r="H343"/>
       <x:c r="I343" t="str">
-        <x:v>airport airspace monitoring</x:v>
+        <x:v>airport c-uas</x:v>
       </x:c>
       <x:c r="J343" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K343" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L343"/>
       <x:c r="M343"/>
@@ -13309,13 +13309,13 @@
       </x:c>
       <x:c r="H344"/>
       <x:c r="I344" t="str">
-        <x:v>runway drone detection</x:v>
+        <x:v>heliport drone detection</x:v>
       </x:c>
       <x:c r="J344" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K344" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L344"/>
       <x:c r="M344"/>
@@ -13347,13 +13347,13 @@
       </x:c>
       <x:c r="H345"/>
       <x:c r="I345" t="str">
-        <x:v>airport counter drone</x:v>
+        <x:v>aviation facility drone security</x:v>
       </x:c>
       <x:c r="J345" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K345" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L345"/>
       <x:c r="M345"/>
@@ -13385,13 +13385,13 @@
       </x:c>
       <x:c r="H346"/>
       <x:c r="I346" t="str">
-        <x:v>border anti drone</x:v>
+        <x:v>border checkpoint anti drone</x:v>
       </x:c>
       <x:c r="J346" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K346" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L346"/>
       <x:c r="M346"/>
@@ -13423,13 +13423,13 @@
       </x:c>
       <x:c r="H347"/>
       <x:c r="I347" t="str">
-        <x:v>border drone detection</x:v>
+        <x:v>border post drone detection</x:v>
       </x:c>
       <x:c r="J347" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K347" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L347"/>
       <x:c r="M347"/>
@@ -13461,13 +13461,13 @@
       </x:c>
       <x:c r="H348"/>
       <x:c r="I348" t="str">
-        <x:v>border c-uas</x:v>
+        <x:v>border patrol c-uas</x:v>
       </x:c>
       <x:c r="J348" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K348" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L348"/>
       <x:c r="M348"/>
@@ -13499,13 +13499,13 @@
       </x:c>
       <x:c r="H349"/>
       <x:c r="I349" t="str">
-        <x:v>border drone detector</x:v>
+        <x:v>customs checkpoint drone detector</x:v>
       </x:c>
       <x:c r="J349" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K349" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L349"/>
       <x:c r="M349"/>
@@ -13537,13 +13537,13 @@
       </x:c>
       <x:c r="H350"/>
       <x:c r="I350" t="str">
-        <x:v>border airspace monitoring</x:v>
+        <x:v>land border anti drone</x:v>
       </x:c>
       <x:c r="J350" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K350" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L350"/>
       <x:c r="M350"/>
@@ -13575,13 +13575,13 @@
       </x:c>
       <x:c r="H351"/>
       <x:c r="I351" t="str">
-        <x:v>border counter drone</x:v>
+        <x:v>coastal border drone detection</x:v>
       </x:c>
       <x:c r="J351" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K351" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L351"/>
       <x:c r="M351"/>
@@ -13613,13 +13613,13 @@
       </x:c>
       <x:c r="H352"/>
       <x:c r="I352" t="str">
-        <x:v>border patrol drone detection</x:v>
+        <x:v>remote border post drone security</x:v>
       </x:c>
       <x:c r="J352" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K352" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L352"/>
       <x:c r="M352"/>
@@ -13651,13 +13651,13 @@
       </x:c>
       <x:c r="H353"/>
       <x:c r="I353" t="str">
-        <x:v>frontier drone monitoring</x:v>
+        <x:v>frontier drone detector</x:v>
       </x:c>
       <x:c r="J353" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K353" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L353"/>
       <x:c r="M353"/>
@@ -13689,13 +13689,13 @@
       </x:c>
       <x:c r="H354"/>
       <x:c r="I354" t="str">
-        <x:v>public safety anti drone</x:v>
+        <x:v>police station anti drone</x:v>
       </x:c>
       <x:c r="J354" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K354" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L354"/>
       <x:c r="M354"/>
@@ -13727,13 +13727,13 @@
       </x:c>
       <x:c r="H355"/>
       <x:c r="I355" t="str">
-        <x:v>public safety drone detection</x:v>
+        <x:v>law enforcement drone detection</x:v>
       </x:c>
       <x:c r="J355" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K355" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L355"/>
       <x:c r="M355"/>
@@ -13765,13 +13765,13 @@
       </x:c>
       <x:c r="H356"/>
       <x:c r="I356" t="str">
-        <x:v>public safety c-uas</x:v>
+        <x:v>emergency command center anti drone</x:v>
       </x:c>
       <x:c r="J356" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K356" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L356"/>
       <x:c r="M356"/>
@@ -13803,13 +13803,13 @@
       </x:c>
       <x:c r="H357"/>
       <x:c r="I357" t="str">
-        <x:v>public safety drone detector</x:v>
+        <x:v>city center drone detector</x:v>
       </x:c>
       <x:c r="J357" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K357" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L357"/>
       <x:c r="M357"/>
@@ -13841,13 +13841,13 @@
       </x:c>
       <x:c r="H358"/>
       <x:c r="I358" t="str">
-        <x:v>law enforcement anti drone</x:v>
+        <x:v>urban security c-uas</x:v>
       </x:c>
       <x:c r="J358" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K358" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L358"/>
       <x:c r="M358"/>
@@ -13879,13 +13879,13 @@
       </x:c>
       <x:c r="H359"/>
       <x:c r="I359" t="str">
-        <x:v>police drone detection</x:v>
+        <x:v>public square drone detection</x:v>
       </x:c>
       <x:c r="J359" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K359" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L359"/>
       <x:c r="M359"/>
@@ -13917,13 +13917,13 @@
       </x:c>
       <x:c r="H360"/>
       <x:c r="I360" t="str">
-        <x:v>emergency response drone monitoring</x:v>
+        <x:v>fire department anti drone</x:v>
       </x:c>
       <x:c r="J360" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K360" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L360"/>
       <x:c r="M360"/>
@@ -13955,13 +13955,13 @@
       </x:c>
       <x:c r="H361"/>
       <x:c r="I361" t="str">
-        <x:v>urban drone security</x:v>
+        <x:v>emergency response drone security</x:v>
       </x:c>
       <x:c r="J361" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K361" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L361"/>
       <x:c r="M361"/>
@@ -13999,7 +13999,7 @@
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K362" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L362"/>
       <x:c r="M362"/>
@@ -14031,13 +14031,13 @@
       </x:c>
       <x:c r="H363"/>
       <x:c r="I363" t="str">
-        <x:v>prison drone detection</x:v>
+        <x:v>correctional facility drone detection</x:v>
       </x:c>
       <x:c r="J363" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K363" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L363"/>
       <x:c r="M363"/>
@@ -14069,13 +14069,13 @@
       </x:c>
       <x:c r="H364"/>
       <x:c r="I364" t="str">
-        <x:v>prison c-uas</x:v>
+        <x:v>jail drone detector</x:v>
       </x:c>
       <x:c r="J364" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K364" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L364"/>
       <x:c r="M364"/>
@@ -14107,13 +14107,13 @@
       </x:c>
       <x:c r="H365"/>
       <x:c r="I365" t="str">
-        <x:v>prison drone detector</x:v>
+        <x:v>detention center anti drone</x:v>
       </x:c>
       <x:c r="J365" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K365" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L365"/>
       <x:c r="M365"/>
@@ -14145,13 +14145,13 @@
       </x:c>
       <x:c r="H366"/>
       <x:c r="I366" t="str">
-        <x:v>prison drone monitoring</x:v>
+        <x:v>prison perimeter c-uas</x:v>
       </x:c>
       <x:c r="J366" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K366" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L366"/>
       <x:c r="M366"/>
@@ -14183,13 +14183,13 @@
       </x:c>
       <x:c r="H367"/>
       <x:c r="I367" t="str">
-        <x:v>correctional facility anti drone</x:v>
+        <x:v>prison contraband drone detection</x:v>
       </x:c>
       <x:c r="J367" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K367" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L367"/>
       <x:c r="M367"/>
@@ -14221,13 +14221,13 @@
       </x:c>
       <x:c r="H368"/>
       <x:c r="I368" t="str">
-        <x:v>contraband drone detection</x:v>
+        <x:v>penitentiary drone security</x:v>
       </x:c>
       <x:c r="J368" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K368" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L368"/>
       <x:c r="M368"/>
@@ -14259,13 +14259,13 @@
       </x:c>
       <x:c r="H369"/>
       <x:c r="I369" t="str">
-        <x:v>prison perimeter drone security</x:v>
+        <x:v>prison drone locator</x:v>
       </x:c>
       <x:c r="J369" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K369" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L369"/>
       <x:c r="M369"/>
@@ -14297,13 +14297,13 @@
       </x:c>
       <x:c r="H370"/>
       <x:c r="I370" t="str">
-        <x:v>port anti drone</x:v>
+        <x:v>seaport anti drone</x:v>
       </x:c>
       <x:c r="J370" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K370" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L370"/>
       <x:c r="M370"/>
@@ -14335,13 +14335,13 @@
       </x:c>
       <x:c r="H371"/>
       <x:c r="I371" t="str">
-        <x:v>port drone detection</x:v>
+        <x:v>harbor drone detection</x:v>
       </x:c>
       <x:c r="J371" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K371" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L371"/>
       <x:c r="M371"/>
@@ -14373,13 +14373,13 @@
       </x:c>
       <x:c r="H372"/>
       <x:c r="I372" t="str">
-        <x:v>port c-uas</x:v>
+        <x:v>container terminal drone detector</x:v>
       </x:c>
       <x:c r="J372" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K372" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L372"/>
       <x:c r="M372"/>
@@ -14411,13 +14411,13 @@
       </x:c>
       <x:c r="H373"/>
       <x:c r="I373" t="str">
-        <x:v>port drone detector</x:v>
+        <x:v>cargo terminal anti drone</x:v>
       </x:c>
       <x:c r="J373" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K373" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L373"/>
       <x:c r="M373"/>
@@ -14449,13 +14449,13 @@
       </x:c>
       <x:c r="H374"/>
       <x:c r="I374" t="str">
-        <x:v>port airspace monitoring</x:v>
+        <x:v>oil port drone detection</x:v>
       </x:c>
       <x:c r="J374" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K374" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L374"/>
       <x:c r="M374"/>
@@ -14487,13 +14487,13 @@
       </x:c>
       <x:c r="H375"/>
       <x:c r="I375" t="str">
-        <x:v>seaport anti drone</x:v>
+        <x:v>port warehouse drone security</x:v>
       </x:c>
       <x:c r="J375" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K375" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L375"/>
       <x:c r="M375"/>
@@ -14525,13 +14525,13 @@
       </x:c>
       <x:c r="H376"/>
       <x:c r="I376" t="str">
-        <x:v>harbor drone detection</x:v>
+        <x:v>port c-uas</x:v>
       </x:c>
       <x:c r="J376" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K376" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L376"/>
       <x:c r="M376"/>
@@ -14563,13 +14563,13 @@
       </x:c>
       <x:c r="H377"/>
       <x:c r="I377" t="str">
-        <x:v>port security drone monitoring</x:v>
+        <x:v>shipping terminal drone detection</x:v>
       </x:c>
       <x:c r="J377" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K377" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L377"/>
       <x:c r="M377"/>
@@ -14601,13 +14601,13 @@
       </x:c>
       <x:c r="H378"/>
       <x:c r="I378" t="str">
-        <x:v>mass event anti drone</x:v>
+        <x:v>stadium anti drone</x:v>
       </x:c>
       <x:c r="J378" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K378" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L378"/>
       <x:c r="M378"/>
@@ -14639,13 +14639,13 @@
       </x:c>
       <x:c r="H379"/>
       <x:c r="I379" t="str">
-        <x:v>mass event drone detection</x:v>
+        <x:v>football stadium drone detection</x:v>
       </x:c>
       <x:c r="J379" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K379" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L379"/>
       <x:c r="M379"/>
@@ -14677,13 +14677,13 @@
       </x:c>
       <x:c r="H380"/>
       <x:c r="I380" t="str">
-        <x:v>mass event c-uas</x:v>
+        <x:v>sports event c-uas</x:v>
       </x:c>
       <x:c r="J380" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K380" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L380"/>
       <x:c r="M380"/>
@@ -14715,13 +14715,13 @@
       </x:c>
       <x:c r="H381"/>
       <x:c r="I381" t="str">
-        <x:v>stadium anti drone</x:v>
+        <x:v>concert drone detector</x:v>
       </x:c>
       <x:c r="J381" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K381" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L381"/>
       <x:c r="M381"/>
@@ -14753,13 +14753,13 @@
       </x:c>
       <x:c r="H382"/>
       <x:c r="I382" t="str">
-        <x:v>stadium drone detection</x:v>
+        <x:v>music festival anti drone</x:v>
       </x:c>
       <x:c r="J382" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K382" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L382"/>
       <x:c r="M382"/>
@@ -14791,13 +14791,13 @@
       </x:c>
       <x:c r="H383"/>
       <x:c r="I383" t="str">
-        <x:v>sports event drone security</x:v>
+        <x:v>convention center drone detection</x:v>
       </x:c>
       <x:c r="J383" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K383" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L383"/>
       <x:c r="M383"/>
@@ -14829,13 +14829,13 @@
       </x:c>
       <x:c r="H384"/>
       <x:c r="I384" t="str">
-        <x:v>concert drone detection</x:v>
+        <x:v>exhibition center anti drone</x:v>
       </x:c>
       <x:c r="J384" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K384" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L384"/>
       <x:c r="M384"/>
@@ -14867,13 +14867,13 @@
       </x:c>
       <x:c r="H385"/>
       <x:c r="I385" t="str">
-        <x:v>crowded event drone detection</x:v>
+        <x:v>large event drone security</x:v>
       </x:c>
       <x:c r="J385" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K385" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L385"/>
       <x:c r="M385"/>
@@ -14905,13 +14905,13 @@
       </x:c>
       <x:c r="H386"/>
       <x:c r="I386" t="str">
-        <x:v>vip anti drone</x:v>
+        <x:v>villa anti drone</x:v>
       </x:c>
       <x:c r="J386" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K386" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L386"/>
       <x:c r="M386"/>
@@ -14943,13 +14943,13 @@
       </x:c>
       <x:c r="H387"/>
       <x:c r="I387" t="str">
-        <x:v>vip drone detection</x:v>
+        <x:v>luxury villa drone detection</x:v>
       </x:c>
       <x:c r="J387" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K387" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L387"/>
       <x:c r="M387"/>
@@ -14981,13 +14981,13 @@
       </x:c>
       <x:c r="H388"/>
       <x:c r="I388" t="str">
-        <x:v>vip c-uas</x:v>
+        <x:v>private estate drone detector</x:v>
       </x:c>
       <x:c r="J388" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K388" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L388"/>
       <x:c r="M388"/>
@@ -15019,13 +15019,13 @@
       </x:c>
       <x:c r="H389"/>
       <x:c r="I389" t="str">
-        <x:v>vip drone detector</x:v>
+        <x:v>mansion anti drone</x:v>
       </x:c>
       <x:c r="J389" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K389" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L389"/>
       <x:c r="M389"/>
@@ -15057,13 +15057,13 @@
       </x:c>
       <x:c r="H390"/>
       <x:c r="I390" t="str">
-        <x:v>private property anti drone</x:v>
+        <x:v>private residence c-uas</x:v>
       </x:c>
       <x:c r="J390" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K390" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L390"/>
       <x:c r="M390"/>
@@ -15095,13 +15095,13 @@
       </x:c>
       <x:c r="H391"/>
       <x:c r="I391" t="str">
-        <x:v>private property drone detection</x:v>
+        <x:v>vip convoy drone security</x:v>
       </x:c>
       <x:c r="J391" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K391" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L391"/>
       <x:c r="M391"/>
@@ -15133,13 +15133,13 @@
       </x:c>
       <x:c r="H392"/>
       <x:c r="I392" t="str">
-        <x:v>vip convoy drone security</x:v>
+        <x:v>yacht anti drone</x:v>
       </x:c>
       <x:c r="J392" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K392" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L392"/>
       <x:c r="M392"/>
@@ -15171,13 +15171,13 @@
       </x:c>
       <x:c r="H393"/>
       <x:c r="I393" t="str">
-        <x:v>private estate drone detection</x:v>
+        <x:v>private ranch drone detection</x:v>
       </x:c>
       <x:c r="J393" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K393" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L393"/>
       <x:c r="M393"/>
@@ -15209,13 +15209,13 @@
       </x:c>
       <x:c r="H394"/>
       <x:c r="I394" t="str">
-        <x:v>enterprise anti drone</x:v>
+        <x:v>mine anti drone</x:v>
       </x:c>
       <x:c r="J394" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K394" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L394"/>
       <x:c r="M394"/>
@@ -15247,13 +15247,13 @@
       </x:c>
       <x:c r="H395"/>
       <x:c r="I395" t="str">
-        <x:v>enterprise drone detection</x:v>
+        <x:v>mining site drone detection</x:v>
       </x:c>
       <x:c r="J395" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K395" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L395"/>
       <x:c r="M395"/>
@@ -15285,13 +15285,13 @@
       </x:c>
       <x:c r="H396"/>
       <x:c r="I396" t="str">
-        <x:v>enterprise c-uas</x:v>
+        <x:v>oil refinery anti drone</x:v>
       </x:c>
       <x:c r="J396" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K396" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L396"/>
       <x:c r="M396"/>
@@ -15323,13 +15323,13 @@
       </x:c>
       <x:c r="H397"/>
       <x:c r="I397" t="str">
-        <x:v>enterprise drone detector</x:v>
+        <x:v>oil field drone detector</x:v>
       </x:c>
       <x:c r="J397" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K397" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L397"/>
       <x:c r="M397"/>
@@ -15361,13 +15361,13 @@
       </x:c>
       <x:c r="H398"/>
       <x:c r="I398" t="str">
-        <x:v>corporate headquarters anti drone</x:v>
+        <x:v>factory drone detection</x:v>
       </x:c>
       <x:c r="J398" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K398" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L398"/>
       <x:c r="M398"/>
@@ -15399,13 +15399,13 @@
       </x:c>
       <x:c r="H399"/>
       <x:c r="I399" t="str">
-        <x:v>corporate campus drone detection</x:v>
+        <x:v>industrial park c-uas</x:v>
       </x:c>
       <x:c r="J399" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K399" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L399"/>
       <x:c r="M399"/>
@@ -15437,13 +15437,13 @@
       </x:c>
       <x:c r="H400"/>
       <x:c r="I400" t="str">
-        <x:v>business campus drone security</x:v>
+        <x:v>corporate headquarters anti drone</x:v>
       </x:c>
       <x:c r="J400" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K400" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L400"/>
       <x:c r="M400"/>
@@ -15475,13 +15475,13 @@
       </x:c>
       <x:c r="H401"/>
       <x:c r="I401" t="str">
-        <x:v>enterprise airspace monitoring</x:v>
+        <x:v>warehouse drone security</x:v>
       </x:c>
       <x:c r="J401" t="str">
         <x:v>Exact match</x:v>
       </x:c>
       <x:c r="K401" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L401"/>
       <x:c r="M401"/>
@@ -15513,13 +15513,13 @@
       </x:c>
       <x:c r="H402"/>
       <x:c r="I402" t="str">
-        <x:v>critical infrastructure anti drone</x:v>
+        <x:v>government building anti drone</x:v>
       </x:c>
       <x:c r="J402" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K402" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L402"/>
       <x:c r="M402"/>
@@ -15551,13 +15551,13 @@
       </x:c>
       <x:c r="H403"/>
       <x:c r="I403" t="str">
-        <x:v>critical infrastructure drone detection</x:v>
+        <x:v>data center drone detection</x:v>
       </x:c>
       <x:c r="J403" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K403" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L403"/>
       <x:c r="M403"/>
@@ -15589,13 +15589,13 @@
       </x:c>
       <x:c r="H404"/>
       <x:c r="I404" t="str">
-        <x:v>critical infrastructure c-uas</x:v>
+        <x:v>telecom tower drone detector</x:v>
       </x:c>
       <x:c r="J404" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K404" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L404"/>
       <x:c r="M404"/>
@@ -15627,13 +15627,13 @@
       </x:c>
       <x:c r="H405"/>
       <x:c r="I405" t="str">
-        <x:v>critical infrastructure drone detector</x:v>
+        <x:v>water treatment plant anti drone</x:v>
       </x:c>
       <x:c r="J405" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K405" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L405"/>
       <x:c r="M405"/>
@@ -15665,13 +15665,13 @@
       </x:c>
       <x:c r="H406"/>
       <x:c r="I406" t="str">
-        <x:v>critical infrastructure airspace monitoring</x:v>
+        <x:v>dam drone detection</x:v>
       </x:c>
       <x:c r="J406" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K406" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L406"/>
       <x:c r="M406"/>
@@ -15703,13 +15703,13 @@
       </x:c>
       <x:c r="H407"/>
       <x:c r="I407" t="str">
-        <x:v>critical infrastructure counter drone</x:v>
+        <x:v>railway station anti drone</x:v>
       </x:c>
       <x:c r="J407" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K407" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L407"/>
       <x:c r="M407"/>
@@ -15741,13 +15741,13 @@
       </x:c>
       <x:c r="H408"/>
       <x:c r="I408" t="str">
-        <x:v>critical facility drone security</x:v>
+        <x:v>metro station drone detector</x:v>
       </x:c>
       <x:c r="J408" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K408" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L408"/>
       <x:c r="M408"/>
@@ -15779,13 +15779,13 @@
       </x:c>
       <x:c r="H409"/>
       <x:c r="I409" t="str">
-        <x:v>critical asset drone monitoring</x:v>
+        <x:v>bridge c-uas</x:v>
       </x:c>
       <x:c r="J409" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K409" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L409"/>
       <x:c r="M409"/>
@@ -15817,13 +15817,13 @@
       </x:c>
       <x:c r="H410"/>
       <x:c r="I410" t="str">
-        <x:v>power plant anti drone</x:v>
+        <x:v>nuclear power plant anti drone</x:v>
       </x:c>
       <x:c r="J410" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K410" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L410"/>
       <x:c r="M410"/>
@@ -15855,13 +15855,13 @@
       </x:c>
       <x:c r="H411"/>
       <x:c r="I411" t="str">
-        <x:v>power plant drone detection</x:v>
+        <x:v>thermal power plant drone detection</x:v>
       </x:c>
       <x:c r="J411" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K411" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L411"/>
       <x:c r="M411"/>
@@ -15893,13 +15893,13 @@
       </x:c>
       <x:c r="H412"/>
       <x:c r="I412" t="str">
-        <x:v>power plant c-uas</x:v>
+        <x:v>hydroelectric power plant drone detector</x:v>
       </x:c>
       <x:c r="J412" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K412" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L412"/>
       <x:c r="M412"/>
@@ -15931,13 +15931,13 @@
       </x:c>
       <x:c r="H413"/>
       <x:c r="I413" t="str">
-        <x:v>power plant drone detector</x:v>
+        <x:v>solar farm anti drone</x:v>
       </x:c>
       <x:c r="J413" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K413" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L413"/>
       <x:c r="M413"/>
@@ -15969,13 +15969,13 @@
       </x:c>
       <x:c r="H414"/>
       <x:c r="I414" t="str">
-        <x:v>power plant airspace monitoring</x:v>
+        <x:v>wind farm drone detection</x:v>
       </x:c>
       <x:c r="J414" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K414" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L414"/>
       <x:c r="M414"/>
@@ -16007,13 +16007,13 @@
       </x:c>
       <x:c r="H415"/>
       <x:c r="I415" t="str">
-        <x:v>energy facility anti drone</x:v>
+        <x:v>power substation drone detector</x:v>
       </x:c>
       <x:c r="J415" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K415" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L415"/>
       <x:c r="M415"/>
@@ -16045,13 +16045,13 @@
       </x:c>
       <x:c r="H416"/>
       <x:c r="I416" t="str">
-        <x:v>power grid drone detection</x:v>
+        <x:v>electric grid c-uas</x:v>
       </x:c>
       <x:c r="J416" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K416" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L416"/>
       <x:c r="M416"/>
@@ -16083,13 +16083,13 @@
       </x:c>
       <x:c r="H417"/>
       <x:c r="I417" t="str">
-        <x:v>substation drone monitoring</x:v>
+        <x:v>power station anti drone</x:v>
       </x:c>
       <x:c r="J417" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K417" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L417"/>
       <x:c r="M417"/>
@@ -16127,7 +16127,7 @@
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K418" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L418"/>
       <x:c r="M418"/>
@@ -16165,7 +16165,7 @@
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K419" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L419"/>
       <x:c r="M419"/>
@@ -16197,13 +16197,13 @@
       </x:c>
       <x:c r="H420"/>
       <x:c r="I420" t="str">
-        <x:v>airport drone detection</x:v>
+        <x:v>runway drone detection</x:v>
       </x:c>
       <x:c r="J420" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K420" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L420"/>
       <x:c r="M420"/>
@@ -16235,13 +16235,13 @@
       </x:c>
       <x:c r="H421"/>
       <x:c r="I421" t="str">
-        <x:v>airport c-uas</x:v>
+        <x:v>airfield drone detector</x:v>
       </x:c>
       <x:c r="J421" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K421" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L421"/>
       <x:c r="M421"/>
@@ -16273,13 +16273,13 @@
       </x:c>
       <x:c r="H422"/>
       <x:c r="I422" t="str">
-        <x:v>airport drone detector</x:v>
+        <x:v>airport perimeter anti drone</x:v>
       </x:c>
       <x:c r="J422" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K422" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L422"/>
       <x:c r="M422"/>
@@ -16311,13 +16311,13 @@
       </x:c>
       <x:c r="H423"/>
       <x:c r="I423" t="str">
-        <x:v>airport airspace monitoring</x:v>
+        <x:v>airport c-uas</x:v>
       </x:c>
       <x:c r="J423" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K423" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L423"/>
       <x:c r="M423"/>
@@ -16349,13 +16349,13 @@
       </x:c>
       <x:c r="H424"/>
       <x:c r="I424" t="str">
-        <x:v>runway drone detection</x:v>
+        <x:v>heliport drone detection</x:v>
       </x:c>
       <x:c r="J424" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K424" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L424"/>
       <x:c r="M424"/>
@@ -16387,13 +16387,13 @@
       </x:c>
       <x:c r="H425"/>
       <x:c r="I425" t="str">
-        <x:v>airport counter drone</x:v>
+        <x:v>aviation facility drone security</x:v>
       </x:c>
       <x:c r="J425" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K425" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L425"/>
       <x:c r="M425"/>
@@ -16425,13 +16425,13 @@
       </x:c>
       <x:c r="H426"/>
       <x:c r="I426" t="str">
-        <x:v>border anti drone</x:v>
+        <x:v>border checkpoint anti drone</x:v>
       </x:c>
       <x:c r="J426" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K426" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L426"/>
       <x:c r="M426"/>
@@ -16463,13 +16463,13 @@
       </x:c>
       <x:c r="H427"/>
       <x:c r="I427" t="str">
-        <x:v>border drone detection</x:v>
+        <x:v>border post drone detection</x:v>
       </x:c>
       <x:c r="J427" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K427" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L427"/>
       <x:c r="M427"/>
@@ -16501,13 +16501,13 @@
       </x:c>
       <x:c r="H428"/>
       <x:c r="I428" t="str">
-        <x:v>border c-uas</x:v>
+        <x:v>border patrol c-uas</x:v>
       </x:c>
       <x:c r="J428" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K428" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L428"/>
       <x:c r="M428"/>
@@ -16539,13 +16539,13 @@
       </x:c>
       <x:c r="H429"/>
       <x:c r="I429" t="str">
-        <x:v>border drone detector</x:v>
+        <x:v>customs checkpoint drone detector</x:v>
       </x:c>
       <x:c r="J429" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K429" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L429"/>
       <x:c r="M429"/>
@@ -16577,13 +16577,13 @@
       </x:c>
       <x:c r="H430"/>
       <x:c r="I430" t="str">
-        <x:v>border airspace monitoring</x:v>
+        <x:v>land border anti drone</x:v>
       </x:c>
       <x:c r="J430" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K430" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L430"/>
       <x:c r="M430"/>
@@ -16615,13 +16615,13 @@
       </x:c>
       <x:c r="H431"/>
       <x:c r="I431" t="str">
-        <x:v>border counter drone</x:v>
+        <x:v>coastal border drone detection</x:v>
       </x:c>
       <x:c r="J431" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K431" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L431"/>
       <x:c r="M431"/>
@@ -16653,13 +16653,13 @@
       </x:c>
       <x:c r="H432"/>
       <x:c r="I432" t="str">
-        <x:v>border patrol drone detection</x:v>
+        <x:v>remote border post drone security</x:v>
       </x:c>
       <x:c r="J432" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K432" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L432"/>
       <x:c r="M432"/>
@@ -16691,13 +16691,13 @@
       </x:c>
       <x:c r="H433"/>
       <x:c r="I433" t="str">
-        <x:v>frontier drone monitoring</x:v>
+        <x:v>frontier drone detector</x:v>
       </x:c>
       <x:c r="J433" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K433" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L433"/>
       <x:c r="M433"/>
@@ -16729,13 +16729,13 @@
       </x:c>
       <x:c r="H434"/>
       <x:c r="I434" t="str">
-        <x:v>public safety anti drone</x:v>
+        <x:v>police station anti drone</x:v>
       </x:c>
       <x:c r="J434" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K434" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L434"/>
       <x:c r="M434"/>
@@ -16767,13 +16767,13 @@
       </x:c>
       <x:c r="H435"/>
       <x:c r="I435" t="str">
-        <x:v>public safety drone detection</x:v>
+        <x:v>law enforcement drone detection</x:v>
       </x:c>
       <x:c r="J435" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K435" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L435"/>
       <x:c r="M435"/>
@@ -16805,13 +16805,13 @@
       </x:c>
       <x:c r="H436"/>
       <x:c r="I436" t="str">
-        <x:v>public safety c-uas</x:v>
+        <x:v>emergency command center anti drone</x:v>
       </x:c>
       <x:c r="J436" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K436" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L436"/>
       <x:c r="M436"/>
@@ -16843,13 +16843,13 @@
       </x:c>
       <x:c r="H437"/>
       <x:c r="I437" t="str">
-        <x:v>public safety drone detector</x:v>
+        <x:v>city center drone detector</x:v>
       </x:c>
       <x:c r="J437" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K437" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L437"/>
       <x:c r="M437"/>
@@ -16881,13 +16881,13 @@
       </x:c>
       <x:c r="H438"/>
       <x:c r="I438" t="str">
-        <x:v>law enforcement anti drone</x:v>
+        <x:v>urban security c-uas</x:v>
       </x:c>
       <x:c r="J438" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K438" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L438"/>
       <x:c r="M438"/>
@@ -16919,13 +16919,13 @@
       </x:c>
       <x:c r="H439"/>
       <x:c r="I439" t="str">
-        <x:v>police drone detection</x:v>
+        <x:v>public square drone detection</x:v>
       </x:c>
       <x:c r="J439" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K439" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L439"/>
       <x:c r="M439"/>
@@ -16957,13 +16957,13 @@
       </x:c>
       <x:c r="H440"/>
       <x:c r="I440" t="str">
-        <x:v>emergency response drone monitoring</x:v>
+        <x:v>fire department anti drone</x:v>
       </x:c>
       <x:c r="J440" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K440" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L440"/>
       <x:c r="M440"/>
@@ -16995,13 +16995,13 @@
       </x:c>
       <x:c r="H441"/>
       <x:c r="I441" t="str">
-        <x:v>urban drone security</x:v>
+        <x:v>emergency response drone security</x:v>
       </x:c>
       <x:c r="J441" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K441" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L441"/>
       <x:c r="M441"/>
@@ -17039,7 +17039,7 @@
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K442" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L442"/>
       <x:c r="M442"/>
@@ -17071,13 +17071,13 @@
       </x:c>
       <x:c r="H443"/>
       <x:c r="I443" t="str">
-        <x:v>prison drone detection</x:v>
+        <x:v>correctional facility drone detection</x:v>
       </x:c>
       <x:c r="J443" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K443" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L443"/>
       <x:c r="M443"/>
@@ -17109,13 +17109,13 @@
       </x:c>
       <x:c r="H444"/>
       <x:c r="I444" t="str">
-        <x:v>prison c-uas</x:v>
+        <x:v>jail drone detector</x:v>
       </x:c>
       <x:c r="J444" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K444" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L444"/>
       <x:c r="M444"/>
@@ -17147,13 +17147,13 @@
       </x:c>
       <x:c r="H445"/>
       <x:c r="I445" t="str">
-        <x:v>prison drone detector</x:v>
+        <x:v>detention center anti drone</x:v>
       </x:c>
       <x:c r="J445" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K445" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L445"/>
       <x:c r="M445"/>
@@ -17185,13 +17185,13 @@
       </x:c>
       <x:c r="H446"/>
       <x:c r="I446" t="str">
-        <x:v>prison drone monitoring</x:v>
+        <x:v>prison perimeter c-uas</x:v>
       </x:c>
       <x:c r="J446" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K446" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L446"/>
       <x:c r="M446"/>
@@ -17223,13 +17223,13 @@
       </x:c>
       <x:c r="H447"/>
       <x:c r="I447" t="str">
-        <x:v>correctional facility anti drone</x:v>
+        <x:v>prison contraband drone detection</x:v>
       </x:c>
       <x:c r="J447" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K447" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L447"/>
       <x:c r="M447"/>
@@ -17261,13 +17261,13 @@
       </x:c>
       <x:c r="H448"/>
       <x:c r="I448" t="str">
-        <x:v>contraband drone detection</x:v>
+        <x:v>penitentiary drone security</x:v>
       </x:c>
       <x:c r="J448" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K448" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L448"/>
       <x:c r="M448"/>
@@ -17299,13 +17299,13 @@
       </x:c>
       <x:c r="H449"/>
       <x:c r="I449" t="str">
-        <x:v>prison perimeter drone security</x:v>
+        <x:v>prison drone locator</x:v>
       </x:c>
       <x:c r="J449" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K449" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L449"/>
       <x:c r="M449"/>
@@ -17337,13 +17337,13 @@
       </x:c>
       <x:c r="H450"/>
       <x:c r="I450" t="str">
-        <x:v>port anti drone</x:v>
+        <x:v>seaport anti drone</x:v>
       </x:c>
       <x:c r="J450" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K450" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L450"/>
       <x:c r="M450"/>
@@ -17375,13 +17375,13 @@
       </x:c>
       <x:c r="H451"/>
       <x:c r="I451" t="str">
-        <x:v>port drone detection</x:v>
+        <x:v>harbor drone detection</x:v>
       </x:c>
       <x:c r="J451" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K451" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L451"/>
       <x:c r="M451"/>
@@ -17413,13 +17413,13 @@
       </x:c>
       <x:c r="H452"/>
       <x:c r="I452" t="str">
-        <x:v>port c-uas</x:v>
+        <x:v>container terminal drone detector</x:v>
       </x:c>
       <x:c r="J452" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K452" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L452"/>
       <x:c r="M452"/>
@@ -17451,13 +17451,13 @@
       </x:c>
       <x:c r="H453"/>
       <x:c r="I453" t="str">
-        <x:v>port drone detector</x:v>
+        <x:v>cargo terminal anti drone</x:v>
       </x:c>
       <x:c r="J453" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K453" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L453"/>
       <x:c r="M453"/>
@@ -17489,13 +17489,13 @@
       </x:c>
       <x:c r="H454"/>
       <x:c r="I454" t="str">
-        <x:v>port airspace monitoring</x:v>
+        <x:v>oil port drone detection</x:v>
       </x:c>
       <x:c r="J454" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K454" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L454"/>
       <x:c r="M454"/>
@@ -17527,13 +17527,13 @@
       </x:c>
       <x:c r="H455"/>
       <x:c r="I455" t="str">
-        <x:v>seaport anti drone</x:v>
+        <x:v>port warehouse drone security</x:v>
       </x:c>
       <x:c r="J455" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K455" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L455"/>
       <x:c r="M455"/>
@@ -17565,13 +17565,13 @@
       </x:c>
       <x:c r="H456"/>
       <x:c r="I456" t="str">
-        <x:v>harbor drone detection</x:v>
+        <x:v>port c-uas</x:v>
       </x:c>
       <x:c r="J456" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K456" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L456"/>
       <x:c r="M456"/>
@@ -17603,13 +17603,13 @@
       </x:c>
       <x:c r="H457"/>
       <x:c r="I457" t="str">
-        <x:v>port security drone monitoring</x:v>
+        <x:v>shipping terminal drone detection</x:v>
       </x:c>
       <x:c r="J457" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K457" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L457"/>
       <x:c r="M457"/>
@@ -17641,13 +17641,13 @@
       </x:c>
       <x:c r="H458"/>
       <x:c r="I458" t="str">
-        <x:v>mass event anti drone</x:v>
+        <x:v>stadium anti drone</x:v>
       </x:c>
       <x:c r="J458" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K458" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L458"/>
       <x:c r="M458"/>
@@ -17679,13 +17679,13 @@
       </x:c>
       <x:c r="H459"/>
       <x:c r="I459" t="str">
-        <x:v>mass event drone detection</x:v>
+        <x:v>football stadium drone detection</x:v>
       </x:c>
       <x:c r="J459" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K459" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L459"/>
       <x:c r="M459"/>
@@ -17717,13 +17717,13 @@
       </x:c>
       <x:c r="H460"/>
       <x:c r="I460" t="str">
-        <x:v>mass event c-uas</x:v>
+        <x:v>sports event c-uas</x:v>
       </x:c>
       <x:c r="J460" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K460" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L460"/>
       <x:c r="M460"/>
@@ -17755,13 +17755,13 @@
       </x:c>
       <x:c r="H461"/>
       <x:c r="I461" t="str">
-        <x:v>stadium anti drone</x:v>
+        <x:v>concert drone detector</x:v>
       </x:c>
       <x:c r="J461" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K461" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L461"/>
       <x:c r="M461"/>
@@ -17793,13 +17793,13 @@
       </x:c>
       <x:c r="H462"/>
       <x:c r="I462" t="str">
-        <x:v>stadium drone detection</x:v>
+        <x:v>music festival anti drone</x:v>
       </x:c>
       <x:c r="J462" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K462" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L462"/>
       <x:c r="M462"/>
@@ -17831,13 +17831,13 @@
       </x:c>
       <x:c r="H463"/>
       <x:c r="I463" t="str">
-        <x:v>sports event drone security</x:v>
+        <x:v>convention center drone detection</x:v>
       </x:c>
       <x:c r="J463" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K463" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L463"/>
       <x:c r="M463"/>
@@ -17869,13 +17869,13 @@
       </x:c>
       <x:c r="H464"/>
       <x:c r="I464" t="str">
-        <x:v>concert drone detection</x:v>
+        <x:v>exhibition center anti drone</x:v>
       </x:c>
       <x:c r="J464" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K464" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L464"/>
       <x:c r="M464"/>
@@ -17907,13 +17907,13 @@
       </x:c>
       <x:c r="H465"/>
       <x:c r="I465" t="str">
-        <x:v>crowded event drone detection</x:v>
+        <x:v>large event drone security</x:v>
       </x:c>
       <x:c r="J465" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K465" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L465"/>
       <x:c r="M465"/>
@@ -17945,13 +17945,13 @@
       </x:c>
       <x:c r="H466"/>
       <x:c r="I466" t="str">
-        <x:v>vip anti drone</x:v>
+        <x:v>villa anti drone</x:v>
       </x:c>
       <x:c r="J466" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K466" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L466"/>
       <x:c r="M466"/>
@@ -17983,13 +17983,13 @@
       </x:c>
       <x:c r="H467"/>
       <x:c r="I467" t="str">
-        <x:v>vip drone detection</x:v>
+        <x:v>luxury villa drone detection</x:v>
       </x:c>
       <x:c r="J467" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K467" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L467"/>
       <x:c r="M467"/>
@@ -18021,13 +18021,13 @@
       </x:c>
       <x:c r="H468"/>
       <x:c r="I468" t="str">
-        <x:v>vip c-uas</x:v>
+        <x:v>private estate drone detector</x:v>
       </x:c>
       <x:c r="J468" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K468" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L468"/>
       <x:c r="M468"/>
@@ -18059,13 +18059,13 @@
       </x:c>
       <x:c r="H469"/>
       <x:c r="I469" t="str">
-        <x:v>vip drone detector</x:v>
+        <x:v>mansion anti drone</x:v>
       </x:c>
       <x:c r="J469" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K469" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L469"/>
       <x:c r="M469"/>
@@ -18097,13 +18097,13 @@
       </x:c>
       <x:c r="H470"/>
       <x:c r="I470" t="str">
-        <x:v>private property anti drone</x:v>
+        <x:v>private residence c-uas</x:v>
       </x:c>
       <x:c r="J470" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K470" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L470"/>
       <x:c r="M470"/>
@@ -18135,13 +18135,13 @@
       </x:c>
       <x:c r="H471"/>
       <x:c r="I471" t="str">
-        <x:v>private property drone detection</x:v>
+        <x:v>vip convoy drone security</x:v>
       </x:c>
       <x:c r="J471" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K471" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L471"/>
       <x:c r="M471"/>
@@ -18173,13 +18173,13 @@
       </x:c>
       <x:c r="H472"/>
       <x:c r="I472" t="str">
-        <x:v>vip convoy drone security</x:v>
+        <x:v>yacht anti drone</x:v>
       </x:c>
       <x:c r="J472" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K472" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L472"/>
       <x:c r="M472"/>
@@ -18211,13 +18211,13 @@
       </x:c>
       <x:c r="H473"/>
       <x:c r="I473" t="str">
-        <x:v>private estate drone detection</x:v>
+        <x:v>private ranch drone detection</x:v>
       </x:c>
       <x:c r="J473" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K473" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L473"/>
       <x:c r="M473"/>
@@ -18249,13 +18249,13 @@
       </x:c>
       <x:c r="H474"/>
       <x:c r="I474" t="str">
-        <x:v>enterprise anti drone</x:v>
+        <x:v>mine anti drone</x:v>
       </x:c>
       <x:c r="J474" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K474" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L474"/>
       <x:c r="M474"/>
@@ -18287,13 +18287,13 @@
       </x:c>
       <x:c r="H475"/>
       <x:c r="I475" t="str">
-        <x:v>enterprise drone detection</x:v>
+        <x:v>mining site drone detection</x:v>
       </x:c>
       <x:c r="J475" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K475" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L475"/>
       <x:c r="M475"/>
@@ -18325,13 +18325,13 @@
       </x:c>
       <x:c r="H476"/>
       <x:c r="I476" t="str">
-        <x:v>enterprise c-uas</x:v>
+        <x:v>oil refinery anti drone</x:v>
       </x:c>
       <x:c r="J476" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K476" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L476"/>
       <x:c r="M476"/>
@@ -18363,13 +18363,13 @@
       </x:c>
       <x:c r="H477"/>
       <x:c r="I477" t="str">
-        <x:v>enterprise drone detector</x:v>
+        <x:v>oil field drone detector</x:v>
       </x:c>
       <x:c r="J477" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K477" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L477"/>
       <x:c r="M477"/>
@@ -18401,13 +18401,13 @@
       </x:c>
       <x:c r="H478"/>
       <x:c r="I478" t="str">
-        <x:v>corporate headquarters anti drone</x:v>
+        <x:v>factory drone detection</x:v>
       </x:c>
       <x:c r="J478" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K478" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L478"/>
       <x:c r="M478"/>
@@ -18439,13 +18439,13 @@
       </x:c>
       <x:c r="H479"/>
       <x:c r="I479" t="str">
-        <x:v>corporate campus drone detection</x:v>
+        <x:v>industrial park c-uas</x:v>
       </x:c>
       <x:c r="J479" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K479" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L479"/>
       <x:c r="M479"/>
@@ -18477,13 +18477,13 @@
       </x:c>
       <x:c r="H480"/>
       <x:c r="I480" t="str">
-        <x:v>business campus drone security</x:v>
+        <x:v>corporate headquarters anti drone</x:v>
       </x:c>
       <x:c r="J480" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K480" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L480"/>
       <x:c r="M480"/>
@@ -18515,13 +18515,13 @@
       </x:c>
       <x:c r="H481"/>
       <x:c r="I481" t="str">
-        <x:v>enterprise airspace monitoring</x:v>
+        <x:v>warehouse drone security</x:v>
       </x:c>
       <x:c r="J481" t="str">
         <x:v>Phrase match</x:v>
       </x:c>
       <x:c r="K481" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="L481"/>
       <x:c r="M481"/>
